--- a/data/crude_oil_sentiment_score_.xlsx
+++ b/data/crude_oil_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12794,6 +12794,2184 @@
         <v>-0.4939</v>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/more-supertankers-divert-u-sanctions-071500362.html</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2025-10-15T07:15:00Z</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>More Supertankers Divert After U.S. Sanctions Hit Chinese Oil Port</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Three very large crude carriers rerouted from China’s Rizhao port after U.S. sanctions targeted the terminal for handling Iranian oil, threatening to disrupt...</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Three very large crude carriers have diverted from their original destination of the port of Rizhao in China, following the U.S. Treasury’s announcement of sanctions on the facility due to its handli… [+2259 chars]</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>-0.3976</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-fall-slightly-risk-035832195.html</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2025-10-10T03:58:32Z</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Oil prices fall slightly as risk premium fades after Gaza deal</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Brent crude futures were down 7 cents at $65.15 a barrel by 0338 GMT.  Israel and the Palestinian militant group Hamas signed a ceasefire agreement on...</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices declined slightly on Friday after settling 1.6% lower in the previous session as the market's risk premium faded after Israel and Hamas agreed to the first phase of a plan to en… [+1944 chars]</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>-0.4105</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>https://ca.news.yahoo.com/trump-says-modi-assured-him-223300956.html</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>By Nandita Bose and Jarrett Renshaw</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2025-10-15T22:33:00Z</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Trump says Modi has assured him India will not buy Russian oil</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>By Nandita Bose and Jarrett Renshaw WASHINGTON (Reuters) -U.S.</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>By Nandita Bose and Jarrett Renshaw
+WASHINGTON (Reuters) -U.S. President Donald Trump said on Wednesday that Indian Prime Minister Narendra Modi has pledged to stop buying oil from Russia, and Trump… [+3143 chars]</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>0.0772</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-says-india-halves-russian-084641073.html</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>By Jarrett Renshaw and Nidhi Verma</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2025-10-17T08:46:41Z</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>US says India halves Russian oil imports, sources say no cuts seen</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>By Jarrett Renshaw and Nidhi Verma WASHINGTON/NEW DELHI (Reuters) -India has halved its purchases of Russian oil, a White House official said, but Indian...</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>By Jarrett Renshaw and Nidhi Verma
+WASHINGTON/NEW DELHI (Reuters) -India has halved its purchases of Russian oil, a White House official said, but Indian sources said no immediate reduction had been… [+3540 chars]</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>-0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-imposes-sanctions-china-refinery-164249899.html</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>By Timothy Gardner</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2025-10-09T16:42:49Z</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>US imposes sanctions on China refinery, others for Iran oil purchases</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>WASHINGTON (Reuters) -The U.S. imposed sanctions on about 100 individuals, entities and vessels, including a Chinese independent refinery and terminal, that ...</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>By Timothy Gardner
+WASHINGTON (Reuters) -The U.S. imposed sanctions on about 100 individuals, entities and vessels, including a Chinese independent refinery and terminal, that helped Iran's oil and … [+1865 chars]</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>-0.1779</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/trump-tariffs-live-updates-white-house-nears-tariff-relief-for-auto-industry-us-deficit-falls-in-first-drop-since-covid-162418171.html</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2025-10-10T16:24:18Z</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Trump tariffs live updates: White House nears tariff relief for auto industry; US deficit falls in first drop since COVID</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Yahoo Finance is chronicling the latest news and updates on President Trump's plans to impose tariffs on goods from other countries.</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>President Trump on Wednesday confirmed that trade tensions with China remain high, telling a reporter who asked whether the two countries are headed for a prolonged trade war, "Well, you're in one no… [+9481 chars]</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>-0.8074</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-dip-trump-putin-064001125.html</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2025-10-17T06:40:01Z</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Oil Prices Dip as Trump-Putin Summit Looms</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Crude oil prices are set for a weekly decline as a potential Trump-Putin summit raises concerns about increased Russian oil exports and a looming supply glut...</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Crude oil prices are set for another weekly decline today, after President Trump announced there were plans to meet with Russia’s Vladimir Putin in a couple of weeks to discuss an end to the war in t… [+2205 chars]</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>-0.8481</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-rebound-trump-claims-013044574.html</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2025-10-16T01:30:44Z</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Oil Prices Rebound After Trump Claims India Will Curb Russian Oil Imports</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Oil prices rose slightly after President Trump claimed India would halt Russian crude imports, though market sentiment remains cautious amid rising...</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Oil prices recovered slightly in early Asian trade on Thursday after a steep drop that pushed WTI and Brent to five-month lows the day before. The rebound was fueled by renewed optimism over U.S. pre… [+2603 chars]</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-drops-below-60-gaza-154819364.html</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2025-10-10T15:48:19Z</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Oil Drops Below $60 on Gaza Ceasefire</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>WTI crude fell below $60 per barrel as easing Middle East tensions and weak China–U.S. sentiment erased much of oil’s geopolitical risk premium.</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>WTI crude fell below $60 per barrel as easing Middle East tensions and weak ChinaU.S. sentiment erased much of oils geopolitical risk premium.
+Friday, October 10, 2025
+The relatively successful imp… [+4952 chars]</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>-0.6808</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-oil-imports-jumped-3-063850587.html</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2025-10-13T06:38:50Z</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>China’s Oil Imports Jumped 3.9% in September</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>China’s crude oil imports rose 3.9% year-on-year in September to 11.5 million barrels per day as refiners ramped up output and the country continued...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Crude oil imports into China last month went up by 3.9% on September 2024, flowing at an average daily rate of some 11.5 million barrels, Reuters calculated, citing official customs data from Beijing… [+2290 chars]</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/3-reliable-dividend-stocks-offering-173152475.html</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Simply Wall St</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2025-10-07T17:31:52Z</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>3 Reliable Dividend Stocks Offering Up To 7.1% Yield</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Amidst recent fluctuations in major stock indexes, with the S&amp;P 500 and Nasdaq reaching new highs before pulling back, investors are increasingly seeking...</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Amidst recent fluctuations in major stock indexes, with the S&amp;amp;P 500 and Nasdaq reaching new highs before pulling back, investors are increasingly seeking stability through dividend stocks. In suc… [+5334 chars]</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>0.2023</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-tariff-threat-pushes-oil-194520634.html</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>By Erwin Seba</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2025-10-10T19:45:20Z</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Trump tariff threat pushes oil to five-month low</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>HOUSTON (Reuters) -Brent and U.S. crude futures fell more than $2 a barrel, or more than 3%, on Friday as U.S. President Donald Trump's threat to impose...</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>By Erwin Seba
+HOUSTON (Reuters) -Brent and U.S. crude futures fell more than $2 a barrel, or more than 3%, on Friday as U.S. President Donald Trump's threat to impose increased tariffs on China cast… [+2412 chars]</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>-0.9136</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-oil-prices-look-strong-200000079.html</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Neil Crosby</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2025-10-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Why Oil Prices Look Strong on Paper but Soft in Reality</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Futures remain backwardated and strong on paper, while physical crude grades show clear signs of weakness.</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Oil markets are struggling to reconcile geopolitics with fundamentals as headlines push prices one way while physical signals pull in the other direction. The result is a market where Brent spreads a… [+3998 chars]</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>-0.3716</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-build-11-oil-storage-083000563.html</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2025-10-07T08:30:00Z</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>China to Build 11 New Oil Storage Sites in 2 Years</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>China is rapidly expanding its oil storage capacity, adding 11 new sites totaling 169 million barrels as it takes advantage of cheap crude and sanctions...</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>China is building new oil storage sites as it stockpiles crude while it is cheap. This year and next will see a total of 11 new storage sites built across the country, Reuters reported today, noting … [+2335 chars]</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-restarts-drilling-offshore-libya-073000957.html</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2025-10-06T07:30:00Z</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Eni Restarts Drilling Work Offshore Libya</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Italy’s Eni has resumed offshore drilling in Libya after a five-year pause, joining other oil majors returning as the country seeks to boost crude output.</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Italy’s Eni has restarted drilling operations offshore Libya after a five-year break prompted by the Covid pandemic.
+The National Oil Corporation of Libya said that the Italian supermajor had starte… [+1848 chars]</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/crude-traders-split-whether-glut-210000784.html</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2025-10-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Crude Traders Split on Whether the Glut Has Arrived</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Bloomberg this week suggested the first signs of oversupply may be emerging already, but a number of analysts disagree</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Predictions of an oil glut have dominated oil market reporting for months. Bloomberg this week suggested the first signs of oversupply may be emerging already, with several million barrels of Middle … [+5467 chars]</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-edge-down-risk-082810941.html</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>By Anna Hirtenstein</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2025-10-10T08:28:10Z</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Oil prices edge down as risk premium fades after Gaza deal</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices declined on Friday, after settling around 1.6% lower in the previous session, as the market's risk premium faded after Israel...</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>By Anna Hirtenstein
+LONDON (Reuters) -Oil prices declined on Friday, after settling around 1.6% lower in the previous session, as the market's risk premium faded after Israel and Hamas agreed to the… [+2491 chars]</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>-0.5106000000000001</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-pushed-down-opec-raises-123147042.html</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Stanislav Bernukhov</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2025-10-06T12:31:47Z</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Oil Is Pushed Down as OPEC+ Raises Production</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>The beginning of October in the financial markets was relatively quiet despite the expected volatility growth.</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>The NFP release was delayed due to the government shutdown in the US, so volatility was muted across the board, as the only important economic driver published was the US services PMI, which was slig… [+2783 chars]</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-fall-risk-premium-140550299.html</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>By Anna Hirtenstein</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2025-10-10T14:05:50Z</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Oil prices fall as risk premium fades after Gaza deal</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices declined to multi-month lows on Friday as the market's risk premium faded after Israel and Hamas agreed to the first phase of a ...</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>By Anna Hirtenstein
+LONDON (Reuters) -Oil prices declined to multi-month lows on Friday as the market's risk premium faded after Israel and Hamas agreed to the first phase of a plan to end the war i… [+2352 chars]</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>-0.7783</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-rises-1-trump-says-071702417.html</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>By Katya Golubkova and Sam Li</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2025-10-16T07:17:02Z</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Oil rises 1% after Trump says India promised to stop buying from Russia</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>TOKYO (Reuters) -Oil prices rose around 1% on Thursday after U. President Donald Trump said Indian Prime Minister Narendra Modi had pledged his country would...</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>By Katya Golubkova and Sam Li
+TOKYO (Reuters) -Oil prices rose around 1% on Thursday after U.S. President Donald Trump said Indian Prime Minister Narendra Modi had pledged his country would stop buy… [+3237 chars]</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>-0.2263</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-set-moderate-dip-065000025.html</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2025-10-10T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Oil Prices Set for Moderate Dip on Gaza Ceasefire</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Oil prices fell below $65 per barrel as a ceasefire between Israel and Hamas removed the Middle East war premium, refocusing markets on oversupply concerns.</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Crude oil prices are on course for another weekly decline following the news of a ceasefire between the Israeli government and Hamas, which was ratified today by Tel Aviv.
+At the time of writing, Br… [+2572 chars]</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>-0.4767</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eia-hikes-us-oil-output-170331599.html</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2025-10-07T17:03:31Z</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>EIA hikes US oil output forecast, warns oversupply will slash prices</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>NEW YORK (Reuters) -U.S. oil production is expected to hit a larger record this year than previously expected, the Energy Information Administration said on ...</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>NEW YORK (Reuters) -U.S. oil production is expected to hit a larger record this year than previously expected, the Energy Information Administration said on Tuesday, even as the agency warned that a … [+1501 chars]</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>-0.3612</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eia-raises-u-oil-output-193000882.html</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Julianne Geiger</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2025-10-07T19:30:00Z</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>EIA Raises U.S. Oil Output Forecast, Warns Oversupply Could Crush Prices</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>The United States is on track to break yet another oil production record this year, but the Energy Information Administration (EIA) says the resulting supply...</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>The United States is on track to break yet another oil production record this year, but the Energy Information Administration (EIA) says the resulting supply glut could drag prices lower in the month… [+2367 chars]</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>-0.2732</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-plunge-u-china-113515115.html</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2025-10-14T11:35:15Z</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Oil Prices Plunge on U.S.-China Trade War Tit-for-Tat</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Oil prices dropped significantly due to escalating trade tensions between the United States and China, fueled by new sanctions and export controls, raising...</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Oil prices wiped out earlier gains to dip by more than 2% in early U.S. trade on Tuesday amid renewed concerns that the trade war between the United States and China could slow global economy.
+As of… [+2508 chars]</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>-0.5574</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-down-market-weighs-excess-094156357.html</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>By Stephanie Kelly</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2025-10-15T09:41:56Z</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Oil down as market weighs excess supply and US-China trade tensions</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices edged lower on Wednesday, as investors weighed the International Energy Agency's prediction of a supply surplus in 2026 and...</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>By Stephanie Kelly
+LONDON (Reuters) -Oil prices edged lower on Wednesday, as investors weighed the International Energy Agency's prediction of a supply surplus in 2026 and trade tensions between the… [+2482 chars]</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>-0.6705</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-chiefs-see-60-oil-000000315.html</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2025-10-16T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Oil Chiefs See $60 Oil as Breaking Point for Shale Growth</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>TotalEnergies and ConocoPhillips warn that U.S. shale output will plateau or decline if WTI stays near $60 a barrel</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Top executives from supermajors, the U.S. shale patch, and national oil companies remain bullish about the oil market in the medium and long term, expecting growing demand and the downturn in oil pri… [+4613 chars]</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/india-turns-guyana-4-million-134056424.html</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Moz Farooque ACCA</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2025-10-17T13:40:56Z</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>India Turns to Guyana for 4 Million Barrels of Exxon Oil</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>First-ever deal marks India's push to diversify crude imports</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>This article first appeared on GuruFocus.
+India is turning to a new oil supplier in Guyana in what's a first-of-its-kind deal that signals how the country is rebalancing its energy imports. Reuters … [+990 chars]</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-edges-us-china-escalate-011915035.html</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>By Anjana Anil</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2025-10-14T01:19:15Z</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Oil edges up as US-China de-escalate trade tensions</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices rose on Tuesday as early signs of a thaw in U.-China trade tensions bolstered market sentiment, alleviating concerns over global fuel...</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>By Anjana Anil
+(Reuters) -Oil prices rose on Tuesday as early signs of a thaw in U.S.-China trade tensions bolstered market sentiment, alleviating concerns over global fuel demand.
+U.S. Treasury Se… [+2266 chars]</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>-0.6249</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-hit-5-month-194533904.html</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2025-10-15T19:45:33Z</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Oil prices hit 5-month low on US-China trade tensions, looming supply surplus</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino NEW YORK (Reuters) -Oil prices eased on Wednesday to a five-month low on escalating U.S.-China trade tensions and the International Energy ...</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino
+NEW YORK (Reuters) -Oil prices eased on Wednesday to a five-month low on escalating U.S.-China trade tensions and the International Energy Agency's prediction of a supply surplus i… [+3539 chars]</t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>-0.7003</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-oil-rig-count-stalls-170836211.html</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Julianne Geiger</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2025-10-17T17:08:36Z</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>US Oil Rig Count Stalls While Output Breaks New Record</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>The total number of active drilling rigs for oil and gas in the United States rose this week, according to new data that Baker Hughes published on Friday.</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>The total number of active drilling rigs for oil and gas in the United States rose this week, according to new data that Baker Hughes published on Friday.
+The total rig count in the US rose this wee… [+1907 chars]</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>0.5859</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-sanctions-hit-serbias-russian-142809961.html</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>By Aleksandar Vasovic and Ivana Sekularac</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2025-10-09T14:28:09Z</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>US sanctions hit Serbia's Russian-owned oil firm NIS</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>BELGRADE (Reuters) -The United States imposed sanctions on Serbia's Russian-owned oil company NIS on Thursday, prompting neighbouring Croatia to cut crude...</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>By Aleksandar Vasovic and Ivana Sekularac
+BELGRADE (Reuters) -The United States imposed sanctions on Serbia's Russian-owned oil company NIS on Thursday, prompting neighbouring Croatia to cut crude s… [+4497 chars]</t>
+        </is>
+      </c>
+      <c r="G379" t="n">
+        <v>-0.5106000000000001</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-tariff-threat-pushes-oil-234413561.html</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>By Erwin Seba</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2025-10-12T23:44:13Z</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Trump tariff threat pushes oil to five-month low</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>(Corrects Brent's settlement at lowest since May 7, not May 5, in paragraph 3)  HOUSTON (Reuters) -Brent and U. crude futures fell more than $2 a barrel, or ...</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>(Corrects Brent's settlement at lowest since May 7, not May 5, in paragraph 3)
+By Erwin Seba
+HOUSTON (Reuters) -Brent and U.S. crude futures fell more than $2 a barrel, or more than 3%, on Friday a… [+2492 chars]</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>-0.8957000000000001</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-declines-gaza-peace-plan-001736277.html</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Mia Gindis and Alex Longley</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2025-10-09T15:51:56Z</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Oil Steadies With Gaza Peace Plan and Risk-Off Mood in Focus</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>West Texas Intermediate fell to trade near $62 a barrel while Brent was above $66.  Israel and Hamas reached a deal for a truce and the release of all...</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Oil edged lower as traders focused on cooling tensions in the Middle East and broader markets struck a more cautious tone.
+West Texas Intermediate fell to trade near $62 a barrel whil… [+2138 chars]</t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>-0.1263</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-rebounds-signs-easing-china-232455752.html</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Paul Burkhardt</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2025-10-13T08:38:48Z</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Oil Rebounds as White House Signals Openness to Deal With China</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>On Sunday, Donald Trump and Vice President JD Vance struck a slightly more conciliatory tone towards China, after an additional 100% tariff and export...</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>(Bloomberg) Oil rose after after the White House signaled openness to reach a deal with China to quell fresh trade tensions between the two biggest crude consumers.
+Brent (BZ=F) advanced above $63 a… [+1946 chars]</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>0.2023</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/iraq-exxon-sign-agreement-help-111630231.html</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2025-10-08T11:16:30Z</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Iraq, Exxon sign agreement to help develop oilfield</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>BAGHDAD (Reuters) -Exxon Mobil signed an agreement with Iraq on Wednesday to help it develop its large Majnoon oilfield and expand its oil export...</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>BAGHDAD (Reuters) -Exxon Mobil signed an agreement with Iraq on Wednesday to help it develop its large Majnoon oilfield and expand its oil export infrastructure, marking a return to the country two y… [+2206 chars]</t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>0.9201</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/iran-oil-boom-continues-powered-000000305.html</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Simon Watkins</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2025-10-15T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Iran’s Oil Boom Continues, Powered by Russian-Chinese Support</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Russia is leading new development efforts in key shared oilfields like Changuleh, Cheshmeh-Khosh, and Arvand.</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Despite ongoing international sanctions and the recent bombing campaign against it by Israel and the U.S., Iran is continuing its push the record levels of oil production it reached in 2024. Accordin… [+9469 chars]</t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/canadian-oil-producers-prioritize-buying-220000967.html</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2025-10-13T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Canadian Oil Producers Prioritize Buying Over Building</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Canada’s oil industry is experiencing a wave of consolidation as producers opt for mergers and acquisitions over new megaprojects, driving record production ...</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>A two-month-long bidding war in Canada’s oil patch signaled there is another way for a company to boost its production and resources than investing in new oil sands production, which is considered th… [+4844 chars]</t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>-0.296</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-steadies-advance-opec-supply-032653872.html</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Omar El Chmouri</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2025-10-07T09:25:03Z</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Oil Snaps Advance With OPEC+ Supply Decision in Focus</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Brent was over $65 a barrel, with West Texas Intermediate below $62.  OPEC and allies including Russia decided at the weekend on a 137,000-barrel-a-day rise,...</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Oil storage tanks at the Sunoco LP Terminal in Crockett, California. Photographer: David Paul Morris/Bloomberg
+(Bloomberg) -- Oil fell following a two-day advance after OPEC+ agreed on a modest supp… [+1487 chars]</t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/matador-resources-mtdr-falls-amid-012719133.html</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:27:19Z</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Matador Resources (MTDR) Falls Amid Declining Oil Prices</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>The share price of Matador Resources Company (NYSE:MTDR) fell by 8.14% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost...</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>The share price of Matador Resources Company (NYSE:MTDR) fell by 8.14% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Matador Resources (M… [+1440 chars]</t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-climb-opec-announces-023550879.html</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2025-10-06T02:35:50Z</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Oil Prices Climb After OPEC+ Announces Modest Output Hike</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>OPEC+ agreed to a cautious 137,000 bpd production hike for November, balancing internal divisions and oversupply concerns while eroding its spare capacity...</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>On Sunday, OPEC+ agreed to raise oil output by 137,000 barrels per day (bpd) from November. The increase is equal to the one adopted in October, with markets seeing it as a cautious step amid persist… [+1786 chars]</t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/houston-american-energy-husa-fell-012625322.html</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:26:25Z</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Houston American Energy (HUSA) Fell By 9% This Week. Here is Why.</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>The share price of Houston American Energy Corp. (NYSEAMERICAN:HUSA) fell by 9.05% between September 26 and October 3, 2025, putting it among the Energy...</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>The share price of Houston American Energy Corp. (NYSEAMERICAN:HUSA) fell by 9.05% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Houston … [+1524 chars]</t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-market-braces-contango-shale-150000859.html</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2025-10-14T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Oil Market Braces for Contango and Shale Slowdown</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>The prospect of a contango is casting a shadow over oil markets, with the entire 2026 WTI futures curve now trading below $60 per barrel</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>The prospect of a contango is casting a shadow over oil markets, with the entire 2026 WTI futures curve now trading below $60 per barrelbeneath breakeven levels for most new shale wells. TotalEnergie… [+6281 chars]</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>0.5367</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/northern-oil-gas-nog-among-012612873.html</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:26:12Z</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Northern Oil and Gas (NOG): Among the Energy Stocks that Fell This Week</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>The share price of Northern Oil and Gas, Inc. (NYSE:NOG) fell by 9.47% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost...</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>The share price of Northern Oil and Gas, Inc. (NYSE:NOG) fell by 9.47% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Northern Oil and Gas… [+1512 chars]</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/sinopec-diverts-supertanker-us-sanctioned-034100552.html</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>By Florence Tan</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2025-10-18T03:41:00Z</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Sinopec diverts supertanker from US-sanctioned port, ship tracking data shows</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>(Corrects October 13 story to remove reference to Sublime China Information research note)  SINGAPORE (Reuters) -The latest U. sanctions on a major Chinese...</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>(Corrects October 13 story to remove reference to Sublime China Information research note)
+By Florence Tan
+SINGAPORE (Reuters) -The latest U.S. sanctions on a major Chinese crude oil terminal have … [+1606 chars]</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/croatia-were-ready-acquire-u-175534228.html</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:55:34Z</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Croatia: We're Ready to Acquire U.S. Sanctioned Serbian Oil Company</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Croatia is ready to acquire Serbia’s Russian-owned oil company NIS, which was hit by U.S. sanctions on Tuesday, Economy Minister Ante Šušnjar announced</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Croatia is ready to acquire Serbia’s Russian-owned oil company NIS, which was hit by U.S. sanctions on Tuesday, Economy Minister Ante Šušnjar announced. The move, he said, would protect Croatia’s sta… [+2442 chars]</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>0.765</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-set-weekly-loss-trump-005937352.html</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>By Nicole Jao</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2025-10-17T00:59:37Z</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Oil set for weekly loss as Trump-Putin summit looms</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices edged lower in early trade on Friday, heading for a weekly loss, with uncertainty over global energy supplies after U. President Donald...</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>By Nicole Jao
+(Reuters) -Oil prices edged lower in early trade on Friday, heading for a weekly loss, with uncertainty over global energy supplies after U.S. President Donald Trump and Russian Presid… [+1748 chars]</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>-0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-set-weekly-loss-trump-070913886.html</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>By Nicole Jao</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2025-10-17T07:09:13Z</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Oil set for weekly loss as Trump-Putin summit looms</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices edged lower on Friday, heading for a weekly loss of nearly 3%, with uncertainty over global energy supplies after U. President Donald...</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>By Nicole Jao
+(Reuters) -Oil prices edged lower on Friday, heading for a weekly loss of nearly 3%, with uncertainty over global energy supplies after U.S. President Donald Trump and Russian Presiden… [+1779 chars]</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>-0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-set-weekly-loss-trump-010150935.html</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>By Nicole Jao</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2025-10-17T01:01:50Z</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Oil set for weekly loss as Trump-Putin summit looms</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices edged lower in early trade on Friday, heading for a weekly loss, with uncertainty over global energy supplies after U. President Donald...</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>By Nicole Jao
+(Reuters) -Oil prices edged lower in early trade on Friday, heading for a weekly loss, with uncertainty over global energy supplies after U.S. President Donald Trump and Russian Presid… [+1748 chars]</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>-0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/north-dakota-oil-heartland-feels-203500631.html</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2025-10-08T20:35:00Z</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>North Dakota Oil Heartland Feels Aftershock of Chevron, Hess Corp. Merger</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>North Dakota’s oil heartland is feeling the aftershocks of Chevron’s $53-billion merger with Hess Corp., as the supermajor trims more than 100 jobs across...</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>North Dakota’s oil heartland is feeling the aftershocks of Chevron’s $53-billion merger with Hess Corp., as the supermajor trims more than 100 jobs across Minot and Tioga. Chevron told Job Service No… [+2376 chars]</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-notches-third-straight-weekly-loss-as-oversupply-worries-grow-203618177.html</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Ines Ferré</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2025-10-17T20:36:18Z</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Oil notches third straight weekly loss as oversupply worries grow</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Oil notched its third straight weekly loss as oversupply fears mount.</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Oil notched its third straight week of losses on Friday as traders grew increasingly concerned about oversupply.
+West Texas Intermediate (CL=F) traded at $57.54 per barrel, while Brent futures (BZ=F… [+1608 chars]</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>-0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/offshore-oil-plan-primed-cash-100000279.html</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Grace Toohey</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2025-10-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Offshore oil plan was 'primed for cash flow,' but then it hit California regulators</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>A Texas company wants to drill for oil off Santa Barbara County's coast. Experts say its path to oil sales is looking more and more challenging.</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Sable Offshore Corp.'s Harmony oil platform off the coast of Refugio State Beach. (Michael Owen Baker / For The Times)
+When a Texas oil company first announced controversial plans to reactivate thre… [+7100 chars]</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>0.3291</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-empire-petroleum-ep-fell-012559182.html</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:25:59Z</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Here is Why Empire Petroleum (EP) Fell This Week</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>The share price of Empire Petroleum Corporation (NYSE:EP) fell by 9.52% between September 26 and October 3, 2025, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>The share price of Empire Petroleum Corporation (NYSE:EP) fell by 9.52% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Here is Why Empire … [+1280 chars]</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/north-sea-oil-booming-norway-220000959.html</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2025-10-15T12:49:00Z</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>North Sea Oil Giants Choose Norway Over Unpredictable UK Market</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>The UK’s windfall tax and scrapped investment allowances have driven out major producers like Ineos and Apache, with 2025 set to be the first year since 1960...</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>The North Sea has become the site of a live policy experiment, showcasing two dramatically different approaches to the energy transition, with profoundly different results.
+While Norway, committed t… [+6553 chars]</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>0.4939</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-slides-sp-500-nasdaq-retreat-from-records-as-rally-takes-another-breather-200146963.html</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2025-10-09T20:01:46Z</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow slides, S&amp;P 500, Nasdaq retreat from records as rally takes another breather</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Investors paused to assess the optimism around AI and interest-rate cuts that has buoyed markets amid the government shutdown.</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Oil prices fell Thursday after President Trump said Wednesday night that Israel and the Palestinian group Hamas have agreed to the "first phase" of a peace plan proposed by the US administration.
+Fu… [+1643 chars]</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>0.7506</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/latest-us-sanctions-iranian-oil-120641837.html</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>By Chen Aizhu, Trixie Yap and Siyi Liu</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2025-10-10T12:06:41Z</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Latest US sanctions on Iranian oil deal blow to China's Sinopec</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>SINGAPORE (Reuters) -The latest U.S. sanctions on Iranian petroleum exports deal a blow to Chinese refining giant Sinopec by targeting a terminal through...</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>By Chen Aizhu, Trixie Yap and Siyi Liu
+SINGAPORE (Reuters) -The latest U.S. sanctions on Iranian petroleum exports deal a blow to Chinese refining giant Sinopec by targeting a terminal through which… [+3809 chars]</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eia-hikes-us-oil-output-175754589.html</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>By Shariq Khan</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2025-10-07T17:57:54Z</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>EIA hikes US oil output forecast, says oversupply will slash prices</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>NEW YORK (Reuters) -U.S. oil production is expected to hit a larger record this year than previously expected, the Energy Information Administration said on ...</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>By Shariq Khan
+NEW YORK (Reuters) -U.S. oil production is expected to hit a larger record this year than previously expected, the Energy Information Administration said on Tuesday, even as the agenc… [+2454 chars]</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-drops-investors-weigh-supply-010255798.html</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>By Sam Li and Jeslyn Lerh</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2025-10-15T01:02:55Z</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Oil drops as investors weigh a supply surplus outlook and US-China trade tensions</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices fell in early trade on Wednesday, extending losses from the previous session, as investors weighed the International Energy Agency's...</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>By Sam Li and Jeslyn Lerh
+(Reuters) -Oil prices fell in early trade on Wednesday, extending losses from the previous session, as investors weighed the International Energy Agency's warning of a supp… [+2021 chars]</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>-0.6908</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-down-market-eyes-excess-042709669.html</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>By Sam Li and Jeslyn Lerh</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2025-10-15T04:27:09Z</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Oil down as market eyes excess supply, US-China trade tensions</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>SINGAPORE (Reuters) -Oil prices fell on Wednesday, extending losses from the previous session, as investors weighed the International Energy Agency's warning...</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>By Sam Li and Jeslyn Lerh
+SINGAPORE (Reuters) -Oil prices fell on Wednesday, extending losses from the previous session, as investors weighed the International Energy Agency's warning of a supply su… [+2337 chars]</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>-0.6908</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/indian-refiners-prepare-cut-russian-090826688.html</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2025-10-16T09:08:26Z</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Indian refiners prepare to cut Russian oil imports, sources say</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma NEW DELHI (Reuters) - Some Indian refiners are preparing to cut Russian oil imports, with expectations of a gradual reduction, three sources...</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma
+NEW DELHI (Reuters) - Some Indian refiners are preparing to cut Russian oil imports, with expectations of a gradual reduction, three sources familiar with the matter told Reuters, wit… [+2771 chars]</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>-0.4767</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-little-changed-investors-weigh-083240472.html</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>By Stephanie Kelly</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2025-10-09T08:32:40Z</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Oil little changed as investors weigh Gaza ceasefire, stalled Ukraine talks</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices were little changed on Thursday as investors weighed a ceasefire deal in Gaza that could ease geopolitical tensions in the...</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>By Stephanie Kelly
+LONDON (Reuters) -Oil prices were little changed on Thursday as investors weighed a ceasefire deal in Gaza that could ease geopolitical tensions in the Middle East against stalled… [+3016 chars]</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/analysis-china-accelerates-oil-build-043841340.html</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2025-10-07T04:38:41Z</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Analysis-China accelerates oil reserve site build amid stockpiling drive</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>State oil companies including Sinopec and CNOOC will add at least 169 million barrels of storage across 11 sites during 2025 and 2026, according to public...</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>(Reuters) -China is building oil reserve sites at a rapid clip as part of a campaign to boost crude stockpiles that increased in urgency after Russia's Ukraine invasion upended global energy flows an… [+5951 chars]</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>0.296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crude_oil_sentiment_score_.xlsx
+++ b/data/crude_oil_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G409"/>
+  <dimension ref="A1:G434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14972,6 +14972,891 @@
         <v>0.296</v>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/sector-surge-2-energy-stocks-153900223.html</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Ethan Feller</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2025-10-24T15:39:00Z</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>This Sector Is About to Surge: 2 Energy Stocks Set to Breakout</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Oil stocks have been one of the quietest sectors this year, but with crude prices rebounding Exxon Mobil and Parr Pacific appear to be compelling...</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Oil prices have been trending lower all year, recently testing a key level of support. But that narrative shifted sharply this week. Following a fresh round of US sanctions targeting Russian oil expo… [+4422 chars]</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>0.5789</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/u-oil-growth-shifts-shale-230000963.html</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2025-10-18T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>U.S. Oil Growth Shifts from Shale to Gulf</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Output is projected to rise from 1.8 to 2.4 million barrels per day by 2027 amid strong federal support and new investment.</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>For over a decade, the shale patch has been the engine behind U.S. oil production growth. Now, the pattern is shifting to offshore oil amid tech advances and maturing shale reservoirs—with the help o… [+5469 chars]</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>0.7845</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/india-nears-deal-slash-us-030616560.html</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2025-10-22T03:06:16Z</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>India nears deal to slash US tariffs on Indian imports to 15%-16%, Mint reports</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>() -India and the United States are nearing a long-stalled trade agreement that would reduce U. tariffs on Indian imports to 15% to 16% from 50%, India's...</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>(Reuters) -India and the United States are nearing a long-stalled trade agreement that would reduce U.S. tariffs on Indian imports to 15% to 16% from 50%, India's Mint reported on Wednesday citing th… [+1473 chars]</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>0.5994</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/massive-u-tariffs-drive-closer-230000925.html</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2025-10-22T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Massive U.S. Tariffs Drive Closer India-Brazil Alliance</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>The two BRICS nations signed new agreements in agriculture, renewable energy, infrastructure, and innovation.</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Two of the founding members of the BRICS alliance, India and Brazil, drew the short straw when it comes to new U.S. trade policy. South America’s largest economy and Asia’s second-biggest economy hav… [+4880 chars]</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>https://uk.finance.yahoo.com/news/gold-price-pound-oil-commodities-currency-latest-083924027.html</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Pedro Goncalves</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2025-10-22T08:39:24Z</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Gold prices bounce back after biggest drop in three years</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Investors have been gripped by gold fever this year, with prices for the precious metal steadily climbing for months.</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Gold prices made a recovery in early European trading, bouncing back after a dramatic 5% plunge in a single session. Bargain hunters swooped in, while a slight dip in the US dollar made the precious … [+4941 chars]</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/brent-bounces-off-60-kazakh-154800477.html</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2025-10-21T15:48:00Z</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Brent Bounces Off $60 as Kazakh Cuts and Asian Demand Lift Prices</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Brent crude bounced back to $61 on Tuesday as Asian crude demand continues to show strength</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>We will then look at some of the key market movers early this week before providing you with the latest analysis of the top news events taking place in the global energy complex over the past few day… [+6554 chars]</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>0.0516</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/market-minute-10-22-25-143000942.html</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>MoneyShow</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2025-10-22T14:30:00Z</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Market Minute 10-22-25- Metals Plunge While Media Talks Heat Up</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Gold and silver gave back more ground in the early going after an intense selloff yesterday. Equities and Treasuries are mostly flat, while crude oil and the...</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Gold and silver gave back more ground in the early going after an intense selloff yesterday. Equities and Treasuries are mostly flat, while crude oil and the dollar are rising modestly.
+To get more … [+1720 chars]</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>-0.3612</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/explainer-russia-war-faces-double-123215541.html</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>By Guy Faulconbridge, Alexander Ershov and Vladimir Soldatkin</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2025-10-23T12:32:15Z</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Explainer-Russia, at war, faces double trouble: Trump ultimatum and a hit to oil sales to India</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>MOSCOW (Reuters) -Russia, the world's second largest oil exporter, is weighing how to respond to U. sanctions on top oil firms Rosneft and Lukoil and the...</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>By Guy Faulconbridge, Alexander Ershov and Vladimir Soldatkin
+MOSCOW (Reuters) -Russia, the world's second largest oil exporter, is weighing how to respond to U.S. sanctions on top oil firms Rosneft… [+4281 chars]</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>-0.7003</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-rises-nearly-5-fresh-133643465.html</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2025-10-23T13:36:43Z</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Oil rises nearly 5% on fresh US sanctions against Russia</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur LONDON (Reuters) -Oil prices rose nearly 5% on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over...</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur
+LONDON (Reuters) -Oil prices rose nearly 5% on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over Russia's war in Ukraine, extending gains f… [+2425 chars]</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>-0.128</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-surges-5-us-sanctions-165751219.html</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2025-10-23T16:57:51Z</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Oil surges 5% after US sanctions Russian firms Rosneft, Lukoil</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U. imposed sanctions on major Russian suppliers Rosneft and Lukoil...</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino
+NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over Russia's war in U… [+3740 chars]</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>-0.6369</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-surges-5-us-sanctions-191410330.html</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2025-10-23T19:14:10Z</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Oil surges 5% after US sanctions Russian firms Rosneft, Lukoil</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U. imposed sanctions on major Russian suppliers Rosneft and Lukoil...</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino
+NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over Moscow's war in U… [+3792 chars]</t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>-0.6369</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-surge-5-us-151820545.html</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2025-10-23T15:18:20Z</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Oil prices surge 5% as US hits Russian firms Rosneft, Lukoil with sanctions</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U. imposed sanctions on major Russian suppliers Rosneft and Lukoil...</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino
+NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over Russia's war in U… [+3595 chars]</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>-0.6369</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-soars-prospects-u-sanctions-204220491.html</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2025-10-22T20:42:20Z</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Oil Soars on Prospects Of New U.S. Sanctions And Surprise Stock Draw</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Oil prices jumped ~3.5% in afternoon trading, extending gains to the highest levels in nearly three weeks as traders reacted to reports that Washington is...</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Oil prices jumped ~3.5% in afternoon trading, extending gains to the highest levels in nearly three weeks as traders reacted to reports that Washington is weighing new sanctions on Russian energy exp… [+2315 chars]</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>0.7783</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/vivakor-signs-term-sheet-40m-114129851.html</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2025-10-22T11:41:29Z</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Vivakor Signs Term Sheet for $40M Commodity Intermediation Credit Facility to Support Crude Oil Trading</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Vivakor Inc. (NASDAQ:VIVK) is one of the Reddit stocks that will go to the moon. On October 15, Vivakor announced the signing of a non-binding term sheet...</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Vivakor Inc. (NASDAQ:VIVK) is one of the Reddit stocks that will go to the moon. On October 15, Vivakor announced the signing of a non-binding term sheet with an undisclosed wholesaler. The agreement… [+1959 chars]</t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-jumps-us-sanctions-russia-222110181.html</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Jack Wittels, Rong Wei Neo and Mia Gindis</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2025-10-23T15:43:39Z</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Oil Jumps as Trump Steps Up Pressure on Russia With Sanctions</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>The US blacklisted Russian oil giants Rosneft PJSC and Lukoil PJSC in an effort to cut off revenue Russia needs for its war in Ukraine.  Senior refinery...</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Oil soared after the US announced sanctions on Russias biggest oil companies, threatening supplies from one of the worlds top producing countries.
+West Texas Intermediate jumped as mu… [+6022 chars]</t>
+        </is>
+      </c>
+      <c r="G424" t="n">
+        <v>-0.5859</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/factbox-us-sanctioned-russian-oil-075837317.html</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2025-10-23T07:58:37Z</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Factbox-US-sanctioned Russian oil majors Rosneft and Lukoil</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>President Donald Trump on Wednesday imposed Ukraine-related sanctions on Russia's largest oil companies, Lukoil and Rosneft, in Washington's toughest...</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>MOSCOW (Reuters) -U.S. President Donald Trump on Wednesday imposed Ukraine-related sanctions on Russia's largest oil companies, Lukoil and Rosneft, in Washington's toughest measures against Russian b… [+1816 chars]</t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>-0.1531</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-oil-futures-little-changed-212309120.html</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Yasin Ebrahim</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2025-10-21T21:23:09Z</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>US oil futures little changed after API reports draw in crude inventories</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Investing.com -- U.S. crude oil futures were little changed from post-settlement levels Tuesday after the American Petroleum Institute reported a fall in...</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Investing.com -- U.S. crude oil futures were little changed from post-settlement levels Tuesday after the American Petroleum Institute reported a fall in domestic crude inventories.
+Crude Oil WTI Fu… [+781 chars]</t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>-0.9413</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/wells-fargo-suggests-2-energy-100031104.html</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2025-10-21T10:00:31Z</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Wells Fargo Suggests 2 Energy Stocks to Buy in a Challenging Market</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>There are headwinds in store for the oil industry, but a new report from Wells Fargo suggests that there are still plenty of sound options for investors. The...</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>There are headwinds in store for the oil industry, but a new report from Wells Fargo suggests that there are still plenty of sound options for investors. The bank sees demand as slowing, although not… [+9362 chars]</t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/glut-hysteria-clashes-missing-oil-000000857.html</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2025-10-23T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Glut Hysteria Clashes with Missing Oil Barrels</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Despite “glut hysteria,” oil prices have ticked higher as traders show fatigue with bearish forecasts and remain sensitive to geopolitical risks.</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>A looming oil glut has taken over the energy commodities market as the dominating sentiment among traders and analysts. Everyone is predicting a glut—the only difference is in its size. But there is … [+5257 chars]</t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>-0.431</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/pump-prices-could-rise-us-164332290.html</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>MATT OTT</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2025-10-23T16:43:32Z</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Pump prices could rise after US, EU hit Russian oil companies with new sanctions and oil spikes</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Oil prices spiked Thursday after the U.S. announced massive new sanctions on Russia's oil industry in an attempt to get Russian President Vladimir Putin to...</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>WASHINGTON (AP) Oil prices spiked Thursday after the U.S. announced massive new sanctions on Russia's oil industry in an attempt to get Russian President Vladimir Putin to the negotiating table and e… [+3082 chars]</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/asian-shares-retreat-crude-prices-054743642.html</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>TERESA CEROJANO</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2025-10-23T05:47:43Z</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Asian shares retreat and crude prices soar $2 after Trump sanctions Russian oil giants</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Shares were mostly lower in Asia on Thursday following a retreat on Wall Street, while crude prices jumped more than $2 after U.S. President Donald Trump...</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>MANILA, Philippines (AP) Shares were mostly lower in Asia on Thursday following a retreat on Wall Street, while crude prices jumped more than $2 after U.S. President Donald Trump announced sanctions … [+3581 chars]</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>-0.5574</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/americas-power-grid-faces-biggest-100048941.html</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2025-10-23T10:00:48Z</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>America's power grid faces its biggest test yet</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Listen and subscribe to Stocks In Translation on Apple Podcasts, Spotify, or wherever you find your favorite podcast. In this episode of Stocks in...</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Welcome to Stocks and Translation, Yahoo Finance's video podcast that cuts through the market mayhem, the noisy numbers, and the hyperbole to give you the information you need to make the right trade… [+27019 chars]</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-seeks-1-million-barrels-193434616.html</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>By Timothy Gardner</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2025-10-21T19:34:34Z</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>US seeks 1 million barrels of oil for Strategic Petroleum Reserve</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Department of Energy said on Tuesday it is looking to buy 1 million barrels of crude oil for delivery to the Strategic Petroleum Reserve, as it seeks to take...</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>By Timothy Gardner
+WASHINGTON (Reuters) -The U.S. Department of Energy said on Tuesday it is looking to buy 1 million barrels of crude oil for delivery to the Strategic Petroleum Reserve, as it seek… [+1872 chars]</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>-0.3818</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/u-funds-tighten-grip-canada-180000594.html</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2025-10-23T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>U.S. Funds Tighten Grip on Canada’s Oil Patch</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>According to McCrea, U.S. funds now own about 59% of Canadian oil and gas companies, up from 56% at the end of 2024, while investments by Canadians have...</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Previously, we reported that the Trump administration has lately been taking over Canada’s rare earths companies as Washington looks to counter Beijing’s dominance in the sector. To wit, Canadian rar… [+5442 chars]</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>0.2023</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-jumps-russia-sanctions-stocks-155846964.html</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>By Caroline Valetkevitch and Amanda Cooper</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2025-10-23T15:58:46Z</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Oil jumps after Russia sanctions; stocks, US yields inch higher</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>NEW YORK/LONDON (Reuters) -Oil prices surged about 5% on Thursday after Washington imposed sanctions on major Russian companies over the Ukraine war, while...</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>By Caroline Valetkevitch and Amanda Cooper
+NEW YORK/LONDON (Reuters) -Oil prices surged about 5% on Thursday after Washington imposed sanctions on major Russian companies over the Ukraine war, while… [+3194 chars]</t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>-0.6369</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crude_oil_sentiment_score_.xlsx
+++ b/data/crude_oil_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G434"/>
+  <dimension ref="A1:G510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15857,6 +15857,2696 @@
         <v>-0.6369</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/indian-refiners-pivot-away-russian-230000877.html</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2025-11-01T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Indian Refiners Pivot Away From Russian Oil</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Indian refiners are shunning Russian oil due to fresh U.S. sanctions, leading to a pivot towards costlier alternatives and potential shifts in global oil...</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Oil prices were little changed in the current week, with bearish sentiment still ruling the markets after the U.S. agreed to a one-year truce to its trade war with China, despite reports that Indian … [+4918 chars]</t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>-0.4215</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/u-invasion-venezuela-mean-global-180000673.html</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Cyril Widdershoven</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2025-11-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>What a U.S. Invasion of Venezuela Would Mean for Global Oil Prices</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>U.S. military preparations near Venezuela risk triggering a geopolitical and energy crisis that could disrupt global oil and gas markets, especially heavy...</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>The risks surrounding Venezuela, the world’s largest oil and gas reserves holder, are clearly skyrocketing. With Venezuela’s president, Maduro, calling upon Russia, China, and Iran to assist in a pos… [+8577 chars]</t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/turkey-buys-more-non-russian-055952081.html</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>By Robert Harvey, Ahmad Ghaddar and Enes Tunagur</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2025-11-03T05:59:52Z</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Turkey buys more non-Russian oil after latest Western sanctions, sources say</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>By Robert Harvey, Ahmad Ghaddar and Enes Tunagur LONDON/MOSCOW (Reuters) -Turkey's largest oil refineries are buying more non-Russian oil in response to the ...</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>By Robert Harvey, Ahmad Ghaddar and Enes Tunagur
+LONDON/MOSCOW (Reuters) -Turkey's largest oil refineries are buying more non-Russian oil in response to the latest Western sanctions on Russia, two p… [+2790 chars]</t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-price-war-now-underway-190000621.html</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Robert Rapier</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2025-11-10T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>A New Oil Price War Is Now Underway</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>OPEC+’s surprise output increase signals a strategic shift from price defense to market-share dominance, reigniting the power struggle with U.S. shale and...</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Contrary to popular belief, oil prices aren’t determined by any one country, company, or cartel. Instead, they’re the product of a global tug-of-war among producers, traders, and policymakers. It’s a… [+5791 chars]</t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>0.0772</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/30-barrel-break-even-project-210000956.html</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Matthew Smith</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2025-11-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>The $30 Barrel Break-Even Project Driving Exxon's Success</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>ExxonMobil's strong third quarter 2025 earnings are significantly driven by rapidly growing, highly profitable production from its world-class Stabroek Block...</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Global energy giant ExxonMobil reported third-quarter 2025 earnings last week. Those results delivered some eye-popping numbers for all the right reasons. The global energy supermajor announced a sol… [+6308 chars]</t>
+        </is>
+      </c>
+      <c r="G439" t="n">
+        <v>0.7845</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-blows-drug-boats-venezuelan-013315461.html</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Patrick FORT</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2025-10-29T01:33:15Z</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>As US blows up drug boats, Venezuelan oil sets sail</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>While the American military blows up boats it claims are transporting drugs from Venezuela, observers say tankers shipping Venezuelan oil in violation of a...</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>The USS Gravely arrived at the Port of Spain on October 26 (Martín Bernetti)
+While the American military blows up boats it claims are transporting drugs from Venezuela, observers say tankers shippin… [+3948 chars]</t>
+        </is>
+      </c>
+      <c r="G440" t="n">
+        <v>-0.3612</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ukrainian-strike-shuts-key-lukoil-170000531.html</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2025-11-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Ukrainian Strike Shuts Key Lukoil Refinery As Sanctions Weigh on Russia</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>A Ukrainian drone strike forced the full suspension of operations at Lukoil's Volgograd refinery, one of Russia’s largest fuel processing hubs, compounding...</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>A Ukrainian drone strike has knocked the Lukoil-operated Volgograd refinery offline, halting one of Russia’s largest fuel processing hubs as Ukraine continues with its campaign to take advantage of M… [+2582 chars]</t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>-0.128</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>https://ca.finance.yahoo.com/news/suncor-ceo-i-honestly-dont-think-we-have-a-true-canadian-peer-172531010.html</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Jeff Lagerquist</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2025-11-05T21:07:29Z</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Suncor CEO: 'I honestly don't think we have a true Canadian peer'</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Upstream production and refinery throughput snapped records in the third quarter.</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Suncor Energy Inc. president and CEO Rich Kruger waits to appear before the House of Commons Standing Committee on Natural Resources in Ottawa, Monday, Oct. 16, 2023. THE CANADIAN PRESS/ Patrick Doyl… [+2787 chars]</t>
+        </is>
+      </c>
+      <c r="G442" t="n">
+        <v>0.9186</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>https://uk.finance.yahoo.com/news/oil-prices-opec-output-gold-pound-latest-101508000.html</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Vicky McKeever</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2025-10-31T10:15:08Z</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Oil prices dip as investors brace for OPEC+ output hike</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Oil prices dipped on Friday, ahead of an anticipated output hike by the Organization of the Petroleum Exporting Countries and its allies.</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Oil prices dipped on Friday morning, ahead of an anticipated output hike by OPEC and its allies (OPEC+).
+Brent crude (BZ=F) futures fell 0.2% to $63.75 per barrel at the time of writing, while West … [+4484 chars]</t>
+        </is>
+      </c>
+      <c r="G443" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-nasdaq-sp-500-dow-come-off-lows-as-rough-week-for-tech-nears-end-201237522.html</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2025-11-07T20:12:37Z</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Stock market today: Nasdaq, S&amp;P 500, Dow rise off lows as rough week for tech nears end</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Markets trimmed losses as investors weighed Musk's $1T pay package and deteriorating jobs data.</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>US stocks came off session lows on Friday as investors weighed bearish consumer sentiment data and odds that the AI investment boom will pay off, while monitoring the ongoing US government shutdown f… [+15240 chars]</t>
+        </is>
+      </c>
+      <c r="G444" t="n">
+        <v>-0.4588</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-end-volatile-week-lower-amid-worst-tech-sell-off-since-april-210026318.html</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2025-11-07T21:00:26Z</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq end volatile week lower amid worst tech sell-off since April</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Markets trimmed losses as investors weighed Musk's $1T pay package and deteriorating jobs data.</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>US stocks came off session lows on Friday as investors weighed bearish consumer sentiment data and odds that the AI investment boom will pay off, while monitoring the ongoing US government shutdown f… [+16110 chars]</t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>-0.8176</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/indias-ongc-eyes-strong-output-185910526.html</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2025-11-11T18:59:10Z</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>India's ONGC Eyes Strong Output Growth Next Year</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>India’s state-run Oil and Natural Gas Corporation (ONGC) expects to produce 21 million metric tonnes (MMT) of crude oil and 21.5 billion cubic meters (BCM...</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>India’s state-run Oil and Natural Gas Corporation (ONGC) expects to produce 21 million metric tonnes (MMT) of crude oil and 21.5 billion cubic meters (BCM) of natural gas in the next fiscal year (FY2… [+2428 chars]</t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>0.7351</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/indian-oil-corp-seeks-replace-074500227.html</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2025-10-30T07:45:00Z</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Indian Oil Corp. Seeks to Replace Russian Oil With American Barrels</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Indian Oil Corp. plans to buy 24 million barrels of crude from the Americas to replace lost Russian supply after new U.S. sanctions disrupted imports and...</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Indian Oil Corp. is looking to buy 24 million barrels of crude oil from the Americas in the first quarter of next year to replace lost Russian supply after the latest U.S. sanctions on Rosneft and Lu… [+2359 chars]</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>-0.7184</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-steadies-narrowing-spreads-point-012331618.html</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Alex Longley and Rong Wei Neo</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2025-11-11T14:08:31Z</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Oil Swings Higher as Fuel Strength Offsets Weak Crude Signals</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>In addition to rising premiums for fuels, technical traders known as commodity trading advisors could potentially spur additional buying in the coming days, ...</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Oil erased an earlier loss to turn higher as signs of a softer crude market were countered by surging premiums for fuels like gasoline and diesel.
+Brebt crude rose toward $65 a barrel… [+2048 chars]</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>-0.891</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_68494ae5-f40d-4894-82a6-0a6395fab303</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2025-10-27T19:04:48Z</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Crude Oil Sees Support from Preliminary US-China Trade Deal</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 237 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>0.3612</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_e0160b98-9540-49fa-880c-4c3154203ed2</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2025-11-06T20:17:44Z</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Crude Oil Prices Slip as Saudi Aramco Cuts Prices</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 237 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/indian-refiner-reliance-offers-rare-104500537.html</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2025-11-06T10:45:00Z</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Indian Refiner Reliance Offers Rare Sale of Middle East Crude</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Reliance Industries is making a rare spot sale of Middle Eastern and Iraqi crude as it pivots away from Russian oil following new U.S. sanctions.</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>India’s Reliance Industries, the top private refiner in the country, is looking to sell some UAE and Iraqi crude in a rare spot market offer, trade sources told Bloomberg on Thursday.
+Reliance has b… [+2339 chars]</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>-0.765</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/indian-refining-giant-switches-russian-065707930.html</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2025-11-03T06:57:07Z</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Indian Refining Giant Switches From Russian to Emirati Crude</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum has purchased a 2-million-barrel cargo of Emirati crude as Indian refiners diversify away from Russian oil following new U.S. sanctions on...</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum, one of the largest refiners in India, has bought a cargo of Emirati Upper Zakum crude, as it seeks alternatives to Russian oil, Reuters has reported, citing unnamed sources.
+The ca… [+2360 chars]</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>-0.8126</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-stable-investors-balance-oversupply-100442375.html</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>By Robert Harvey</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2025-11-11T10:04:42Z</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Oil stable as investors balance oversupply worries with sanctions risks</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices were stable on Tuesday, as oversupply concerns balanced uncertainty over the impact of the latest U. Brent crude futures rose 27...</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>By Robert Harvey
+LONDON (Reuters) -Oil prices were stable on Tuesday, as oversupply concerns balanced uncertainty over the impact of the latest U.S. sanctions on Russian oil.
+Brent crude futures ro… [+2045 chars]</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>-0.765</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/india-ongc-net-profit-slips-103258238.html</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2025-11-11T10:32:58Z</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>India’s ONGC Net Profit Slips 18% as Oil Prices Drop</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>ONGC’s second-quarter profit fell 17.8% year-on-year due to weaker crude prices, even as India’s top oil and gas producer pushed ahead with new discoveries...</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Indian state-owned Oil and Natural Gas Corporation Limited (ONGC), the biggest oil and gas explorer and producer in the country, booked a 17.8% decline in its net profit for the July-September quarte… [+2387 chars]</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-gains-us-government-shutdown-094057321.html</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2025-11-10T09:40:57Z</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Oil gains on US government shutdown optimism</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices rose on Monday on optimism that the U. government shutdown could end soon and lift demand in ​the world's top oil consumer...</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur
+LONDON (Reuters) -Oil prices rose on Monday on optimism that the U.S. government shutdown could end soon and lift demand in the world's top oil consumer, offsetting concerns about ri… [+2018 chars]</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>0.8658</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/saudi-arabia-poised-cut-oil-103245706.html</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2025-10-31T10:32:45Z</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Poised to Cut Oil Prices for Asia Amid OPEC+ Output Rise</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Saudi Arabia is expected to lower its official selling prices for crude oil to Asia in December as supply increases, though uncertainty around Russian...</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Increasing supply and weaker Middle Eastern benchmark prices will likely prompt Saudi Arabia to cut the official selling prices for its crude loading for Asia in December, but a scramble for non-Russ… [+2421 chars]</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>-0.5994</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/consumers-feel-pinch-pump-russia-123000588.html</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Jack Wittels, Veena Ali-Khan, Nicholas Lua and Nathan Risser</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2025-11-15T12:30:00Z</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Consumers Feel Pinch at Pump as Russia Drives Oil Refining Boom</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>In Europe, the US and Asia, giant plants are making money by doing what they’ve always done: converting crude oil into vital fuels and selling them at a...</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>The Valero Houston refinery. Valero Energy Corp. and Turkiye Petrol Rafinerileri AS have seen stellar rises, while Orlen SA gained more than 100% year-to-date.
+(Bloomberg) -- Its a great time to be … [+5745 chars]</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>0.8316</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/market-minute-11-11-25-142000701.html</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>MoneyShow</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2025-11-11T14:20:00Z</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Market Minute 11-11-25- Shutdown Ending, But AI Debate Heating Up</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Happy Veterans Day! Stocks are mostly flat after a big relief rally on Monday. Gold, silver, and crude oil are rallying, though, while the dollar is slipping...</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Happy Veterans Day! Stocks are mostly flat after a big relief rally on Monday. Gold, silver, and crude oil are rallying, though, while the dollar is slipping.
+The Senate secured another vote needed … [+2080 chars]</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>0.8398</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/market-minute-10-29-25-141500219.html</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>MoneyShow</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2025-10-29T14:15:00Z</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Market Minute 10-29-25- Tech Towers Over Markets as NVDA Tops $5 TLN</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Stocks are modestly higher after a rally Tuesday that lacked breadth. Gold and silver are bouncing after a big multi-day selloff, while crude oil, Treasuries...</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Stocks are modestly higher after a rally Tuesday that lacked breadth. Gold and silver are bouncing after a big multi-day selloff, while crude oil, Treasuries, and the dollar are mostly flat ahead of … [+2249 chars]</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/market-minute-11-3-25-142000392.html</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>MoneyShow</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2025-11-03T14:20:00Z</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Market Minute 11-3-25- Kimberly-Kenvue Ink $40 BLN Deal</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Stocks are mixed in the early going after last week’s solid finish. Gold and silver are rising modestly, while the dollar, Treasuries, and crude oil are...</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Stocks are mixed in the early going after last weeks solid finish. Gold and silver are rising modestly, while the dollar, Treasuries, and crude oil are mostly flat.
+Consumer products giant Kimberly-… [+1685 chars]</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>-0.296</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/india-races-replace-russian-oil-103000803.html</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2025-11-10T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>India Races to Replace Russian Oil With U.S., Iraqi, and UAE Crude</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>India’s refiners are rushing to buy U.S., Iraqi, and UAE crude to offset losses from new sanctions on Russian oil exports.</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Two Indian refiners bought a total of 5 million barrels of crude oil from the United States, Iraq, and the UAE on the spot market as they seek alternatives to Russian crude.
+Reuters reported, citing… [+2322 chars]</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>-0.8519</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/brent-stalls-65-markets-shrug-160000783.html</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2025-11-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Brent Stalls at $65 as Markets Shrug Off OPEC+ Supply Signals</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>OPEC+’s efforts to calm fears of a 2026 oil glut failed to move crude prices, which remain flat near $65 per barrel amid subdued sentiment.</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>OPEC+ has failed to spark an oil price rally with its commitment to halt production hikes in the first quarter of 2026, as fears of a supply glut continue to weigh on both Brent and WTI.
+Oil prices
+… [+7364 chars]</t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>-0.3818</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/australia-woodside-bets-big-lng-081017859.html</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2025-11-05T08:10:17Z</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Australia’s Woodside Bets Big on LNG Boom With 2032 Growth Plan</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Woodside Energy plans to boost oil and gas sales by 50% by 2032 through major LNG and crude expansion projects across Australia, the U.S., and Mexico.</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Australia’s Woodside Energy expects its sales of crude oil and natural gas to rise by some 50% by 2032, driven by growing demand for energy, especially in Asia.
+Growing at an annual rate of 6%, sale… [+2162 chars]</t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>0.6969</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/washington-oil-sanctions-rattle-asia-210000361.html</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2025-10-26T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Washington’s Oil Sanctions Rattle Asia’s Energy Security</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>The supply security of some major Asian importers just got problematic.</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>The U.S. federal government this week declared sanctions on two of the largest Russian crude oil exporters, Rosneft and Lukoil, which together account for about half of the country’s total outflows. … [+5313 chars]</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/morgan-stanley-first-revise-oil-090000678.html</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2025-11-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Morgan Stanley First to Revise Oil Price Forecast After OPEC+ Update</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Morgan Stanley raised its 2026 Brent crude forecast to $60 per barrel after OPEC+ paused production hikes, signaling market stabilization amid ongoing...</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Morgan Stanley raised its price forecast for Brent crude for 2026 to $60 per barrel from $57.50 following OPEC+’s decision to pause production hikes over the first three months of next year.
+This wa… [+2298 chars]</t>
+        </is>
+      </c>
+      <c r="G465" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/floating-oil-storage-surge-puts-000000542.html</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2025-11-16T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Floating Oil Storage Surge Puts Market Balance on Edge</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Analysts warn that if these stranded barrels find buyers, oil markets could tip into deep oversupply.</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>A shadow fleet is quietly swelling across the world’s oceans, packed with sanctioned barrels from Russia, Iran, and Venezuela. For now, those tankers have kept to the sidelines of the global market—b… [+5244 chars]</t>
+        </is>
+      </c>
+      <c r="G466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-slips-oversupply-concerns-stronger-132150760.html</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>By Seher Dareen</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2025-11-04T13:21:50Z</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Oil slips on oversupply concerns, stronger dollar</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>By Seher Dareen LONDON (Reuters) -Oil prices fell over 1% on Tuesday as OPEC+'s decision to pause output hikes in the first quarter next year along with weak...</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>By Seher Dareen
+LONDON (Reuters) -Oil prices fell over 1% on Tuesday as OPEC+'s decision to pause output hikes in the first quarter next year along with weak manufacturing data and a stronger dollar… [+2051 chars]</t>
+        </is>
+      </c>
+      <c r="G467" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-slips-oversupply-concerns-stronger-092558834.html</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>By Seher Dareen</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2025-11-04T09:25:58Z</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Oil slips on oversupply concerns, stronger dollar</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices fell over 1% on Tuesday as OPEC+'s decision to pause output hikes in the first quarter next year along with weak manufacturing...</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>By Seher Dareen
+LONDON (Reuters) -Oil prices fell over 1% on Tuesday as OPEC+'s decision to pause output hikes in the first quarter next year along with weak manufacturing data and a stronger dollar… [+2109 chars]</t>
+        </is>
+      </c>
+      <c r="G468" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-steadies-us-china-trade-160540957.html</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2025-10-27T16:05:40Z</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Oil steadies as US-China trade deal hope, Russian sanctions counter demand concerns</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>HOUSTON (Reuters) -Oil prices held steady on Monday as hopes of a trade deal framework between the U. sanctions on Russia offset broader concerns about weak ...</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar
+HOUSTON (Reuters) -Oil prices held steady on Monday as hopes of a trade deal framework between the U.S. and China and renewed U.S. sanctions on Russia offset broader concerns ab… [+2396 chars]</t>
+        </is>
+      </c>
+      <c r="G469" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-slip-despite-lukoil-060500613.html</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2025-11-11T06:05:00Z</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Oil Prices Slip Despite Lukoil Declaring Force Majeure in Iraq</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Oil prices fell despite Lukoil declaring force majeure on its Iraqi operations after new U.S. sanctions, as traders focused on signs of global oversupply...</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Crude oil prices opened lower today even after Russia’s Lukoil declared force majeure on its operations in one of Iraq’s biggest oil fields because of the latest U.S. sanctions.
+At the time of writi… [+2266 chars]</t>
+        </is>
+      </c>
+      <c r="G470" t="n">
+        <v>-0.7096</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-falls-investors-weigh-potential-184105714.html</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2025-11-06T18:41:05Z</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Oil falls as investors weigh potential supply glut, weak demand</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>HOUSTON (Reuters) -Oil prices declined on Thursday as investors considered a potential supply glut, as well as weakened demand in the United States, the...</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney
+HOUSTON (Reuters) -Oil prices declined on Thursday as investors considered a potential supply glut, as well as weakened demand in the United States, the world's largest oil con… [+2511 chars]</t>
+        </is>
+      </c>
+      <c r="G471" t="n">
+        <v>-0.3182</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-posts-biggest-drop-since-202603193.html</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Mia Gindis and Veena Ali-Khan</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2025-11-12T20:26:03Z</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Oil Posts Biggest Drop Since June Amid Supply Glut Concerns</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>West Texas Intermediate fell by 4.2% to settle around $58.50 a barrel, wiping out three sessions of gains.  The US benchmark’s nearest timespread briefly...</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Oil dropped by the most since June as a key market gauge flashed weakness and OPEC said global crude supplies surpassed demand sooner than anticipated.
+West Texas Intermediate fell by… [+2275 chars]</t>
+        </is>
+      </c>
+      <c r="G472" t="n">
+        <v>-0.8442</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-dip-oversupply-concerns-110000201.html</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2025-10-27T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Oil Prices Dip As Oversupply Concerns Mount</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Oil prices eased on Monday amid concerns of looming oversupply, despite last week's rally spurred by sanctions on Russian oil producers and positive US-China...</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Oil prices gave up earlier gains to turn 1% lower on Monday amid profit-taking following last week’s rally.
+As of 7:13 a.m. ET, the U.S. benchmark, WTI Crude, traded 0.81% lower at $60.98. The inter… [+2367 chars]</t>
+        </is>
+      </c>
+      <c r="G473" t="n">
+        <v>-0.6908</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-fall-us-china-112114344.html</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>By Seher Dareen</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2025-10-27T11:21:14Z</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Oil prices fall after US and China reach trade deal framework</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>By Seher Dareen LONDON (Reuters) -Oil prices fell on Monday, pressured by scepticism that a U.S. and Chinese trade deal framework would immediately boost oil...</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>By Seher Dareen
+LONDON (Reuters) -Oil prices fell on Monday, pressured by scepticism that a U.S. and Chinese trade deal framework would immediately boost oil demand and after Iraq's oil minister con… [+2205 chars]</t>
+        </is>
+      </c>
+      <c r="G474" t="n">
+        <v>-0.1027</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-stabilizes-selloff-amid-opec-161500615.html</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2025-11-13T16:15:00Z</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Oil Stabilizes After Selloff Amid OPEC Reassessment and U.S. Funding Deal</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Oil prices steadied on Wednesday after a sharp 4% slide the day before, with Brent trading near $63.08 and WTI around $58.80 at 11:01 a.m. ET, as traders...</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Oil prices steadied on Wednesday after a sharp 4% slide the day before, with Brent trading near $63.08 and WTI around $58.80 at 11:01 a.m. ET, as traders reassessed the latest OPEC shift toward a mor… [+2547 chars]</t>
+        </is>
+      </c>
+      <c r="G475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-slips-oversupply-concerns-stronger-141838212.html</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>By Seher Dareen</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2025-11-04T14:18:38Z</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Oil slips on oversupply concerns and stronger dollar</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices fell more than 1% on Tuesday as the OPEC+ decision to pause output hikes in the first quarter of next year, along with weak...</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>By Seher Dareen
+LONDON (Reuters) -Oil prices fell more than 1% on Tuesday as the OPEC+ decision to pause output hikes in the first quarter of next year, along with weak manufacturing data and a stro… [+2049 chars]</t>
+        </is>
+      </c>
+      <c r="G476" t="n">
+        <v>-0.0772</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-settles-lower-stronger-dollar-203722460.html</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2025-11-04T20:37:22Z</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Oil settles lower on stronger dollar, fears of oversupply</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar HOUSTON (Reuters) -Oil prices settled lower on Tuesday as weaker manufacturing numbers and a stronger dollar weighed on demand, while...</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar
+HOUSTON (Reuters) -Oil prices settled lower on Tuesday as weaker manufacturing numbers and a stronger dollar weighed on demand, while the OPEC+ decision to pause output hikes in… [+2497 chars]</t>
+        </is>
+      </c>
+      <c r="G477" t="n">
+        <v>-0.6597</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-unmoved-trump-xi-193100458.html</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2025-10-31T19:31:00Z</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Oil Prices Unmoved by Trump-Xi Meeting</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>This report provides an overview of global oil and natural gas market trends, including price changes, production data, and geopolitical developments...</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>This report provides an overview of global oil and natural gas market trends, including price changes, production data, and geopolitical developments impacting energy.
+The Trump-Xi meeting in South … [+4931 chars]</t>
+        </is>
+      </c>
+      <c r="G478" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-oil-drilling-picks-baker-181111747.html</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Julianne Geiger</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2025-11-14T18:11:11Z</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>US Oil Drilling Picks Up: Baker Hughes</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>The total number of active drilling rigs for oil and gas in the United States rose this week, according to new data that Baker Hughes published on Friday.</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>The total number of active drilling rigs for oil and gas in the United States rose this week, according to new data that Baker Hughes published on Friday.
+The total rig count in the US rose by 1 to … [+1962 chars]</t>
+        </is>
+      </c>
+      <c r="G479" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-steadies-us-china-trade-133752303.html</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>By Seher Dareen</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2025-10-27T13:37:52Z</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Oil steadies as US-China trade deal hopes counter demand concerns</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>LONDON (Reuters) -Oil prices recovered from early losses on Monday as optimism over a trade deal framework between the U. and China countered concerns about ...</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>By Seher Dareen
+LONDON (Reuters) -Oil prices recovered from early losses on Monday as optimism over a trade deal framework between the U.S. and China countered concerns about weak demand for crude.
+… [+2168 chars]</t>
+        </is>
+      </c>
+      <c r="G480" t="n">
+        <v>-0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-falls-1-barrel-investors-151551368.html</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2025-10-28T15:15:51Z</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Oil falls $1 a barrel as investors weigh Russia sanctions, OPEC+ output plans</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>HOUSTON (Reuters) -Oil prices slipped around $1 a barrel on Tuesday and were on track for a third straight day of declines as investors considered the impact...</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney
+HOUSTON (Reuters) -Oil prices slipped around $1 a barrel on Tuesday and were on track for a third straight day of declines as investors considered the impact of U.S. sanctions … [+2349 chars]</t>
+        </is>
+      </c>
+      <c r="G481" t="n">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exclusive-turkey-buys-more-non-101958477.html</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>By Robert Harvey, Ahmad Ghaddar and Enes Tunagur</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2025-11-02T10:19:58Z</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Exclusive-Turkey buys more non-Russian oil after latest Western sanctions, sources say</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>By Robert Harvey, Ahmad Ghaddar and Enes Tunagur LONDON/MOSCOW (Reuters) -Turkey's largest oil refineries are buying more non-Russian oil in response to the ...</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>By Robert Harvey, Ahmad Ghaddar and Enes Tunagur
+LONDON/MOSCOW (Reuters) -Turkey's largest oil refineries are buying more non-Russian oil in response to the latest Western sanctions on Russia, two p… [+2790 chars]</t>
+        </is>
+      </c>
+      <c r="G482" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-steady-three-day-drop-003233394.html</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Bloomberg News</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2025-10-29T10:37:39Z</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Oil Steady After Three-Day Drop With Focus on Russia, Stockpiles</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Brent traded above $64 a barrel, while West Texas Intermediate was near $60.  US President Donald Trump will follow through and enforce harsh new sanctions...</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Oil storage tanks in Yokohama, Japan. Photographer: Soichiro Koriyama/Bloomberg
+(Bloomberg) -- Oil held a three-day drop as investors assessed the impact of Western sanctions against leading Russian… [+1765 chars]</t>
+        </is>
+      </c>
+      <c r="G483" t="n">
+        <v>-0.4939</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-slips-nasdaq-pops-as-ai-optimism-sends-amazon-nvidia-higher-210217774.html</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2025-11-03T21:02:17Z</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow slips, Nasdaq pops as AI optimism sends Amazon, Nvidia higher</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>US stocks made gains, with Wall Street looking to maintain upward momentum.</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Eight leading member nations of OPEC+, a group of major oil producers, agreed on Sunday to raise production by 137,000 barrels per day (b/d) in December but signaled a pause in rate changes through t… [+1870 chars]</t>
+        </is>
+      </c>
+      <c r="G484" t="n">
+        <v>0.4854</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-falls-2-investors-weigh-162403896.html</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2025-10-28T16:24:03Z</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Oil falls 2% as investors weigh Russia sanctions, OPEC+ output plans</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney HOUSTON (Reuters) -Oil prices slipped about 2% on Tuesday and were on track for a third straight day of declines as investors...</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney
+HOUSTON (Reuters) -Oil prices slipped about 2% on Tuesday and were on track for a third straight day of declines as investors considered the impact of U.S. sanctions against Ru… [+3241 chars]</t>
+        </is>
+      </c>
+      <c r="G485" t="n">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/markets-scramble-assess-size-oil-010000648.html</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2025-11-05T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Markets Scramble to Assess the Size of the Oil Glut</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>The oil market is bracing for a significant oversupply due to surging supply, subdued demand, and US sanctions on Russian producers, leading to varying...</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>For months, the oil market has been bracing itself for a looming large oversupply. Forecasters, investment banks, and analysts expect the overhang to depress oil prices at the end of this year and ea… [+5879 chars]</t>
+        </is>
+      </c>
+      <c r="G486" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chevron-beats-estimates-hess-deal-101504729.html</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Kevin Crowley</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2025-10-31T10:15:04Z</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Chevron Beats Estimates as Hess Deal Helps Boost Oil Production</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Adjusted, third-quarter earnings of $1.85 a share exceeded the $1.66 average forecast in a Bloomberg survey of analysts.  International oil prices are on...</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Chevron Corp. beat earnings estimates as profits from the $53 billion Hess Corp. acquisition were included in the results for the first time, boosting oil production and cash flow.
+Ad… [+2246 chars]</t>
+        </is>
+      </c>
+      <c r="G487" t="n">
+        <v>0.8625</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/phillips-66-psx-q3-earnings-213002034.html</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Zacks Equity Research</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2025-11-07T21:30:02Z</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Phillips 66 (PSX) Q3 Earnings: Taking a Look at Key Metrics Versus Estimates</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Although the revenue and EPS for Phillips 66 (PSX) give a sense of how its business performed in the quarter ended September 2025, it might be worth...</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>For the quarter ended September 2025, Phillips 66 (PSX) reported revenue of -$999 million, down 102.8% over the same period last year. EPS came in at $2.52, compared to $2.04 in the year-ago quarter.… [+2986 chars]</t>
+        </is>
+      </c>
+      <c r="G488" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-big-oil-still-gushing-010000927.html</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2025-11-13T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Why Big Oil Is Still Gushing Profits Despite Low Oil Prices</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Despite oil prices trading about $15/bbl below their 52-week highs, Big Oil firms—Exxon, Chevron, Shell, and TotalEnergies—collectively earned over $21...</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Oil markets have been volatile over the past couple of weeks, driven by a series of geopolitical developments including new U.S. sanctions on Russian energy, coupled with a fragile cease-fire in Gaza… [+5849 chars]</t>
+        </is>
+      </c>
+      <c r="G489" t="n">
+        <v>0.7017</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chevrons-hess-acquisition-boosts-q3-183000792.html</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2025-10-31T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Chevron's Hess Acquisition Boosts Q3 Output Beyond Expectations</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Chevron reported stronger-than-expected third-quarter results, driven by record oil and gas production following its $53-billion acquisition of Hess...</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Chevron reported stronger-than-expected third-quarter results on Friday, supported by record oil and gas production following its roughly $53-billion acquisition of Hess Corporation. The U.S. superma… [+2841 chars]</t>
+        </is>
+      </c>
+      <c r="G490" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/libya-ships-first-ever-cargo-093000516.html</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2025-11-13T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Libya Ships First-Ever Cargo From Long-Stalled Chadar Oil Field</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Libya’s Zallaf Oil and Gas has shipped the first 600,000-barrel export cargo from the long-delayed Chadar field amid a wave of new discoveries and returning ...</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Libyan company Zallaf Oil and Gas has shipped the first export cargo from the Chadar oil field, at 600,000 barrels.
+Production at the field started in January this year from five wells, Reuters repo… [+2232 chars]</t>
+        </is>
+      </c>
+      <c r="G491" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/markets-lay-low-ahead-fed-104020526.html</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Stanislav Bernukhov</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2025-10-28T10:40:20Z</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Markets Lay Low Ahead of the FED</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>The financial markets are stabilizing ahead of the FED’s meeting.</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>The US inflation was published despite the government shutdown in the US and was a bit softer than anticipated, which had caused the immediate bullish reaction of Gold, stock indices, and pushed down… [+3333 chars]</t>
+        </is>
+      </c>
+      <c r="G492" t="n">
+        <v>-0.2732</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/russian-oil-tanker-turns-back-093000237.html</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2025-10-29T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Russian Oil Tanker Turns Back Under U.S. Sanctions Threat</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>A Russian oil tanker bound for India has reversed course in the Baltic Sea following new U.S. sanctions on Rosneft and Lukoil, disrupting crude flows but...</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>An Aframax tanker carrying Russian crude to India has reversed course soon after leaving the Russian coast and is currently idling in the Baltic Sea, Kpler has reported, as cited by Bloomberg. The cr… [+2670 chars]</t>
+        </is>
+      </c>
+      <c r="G493" t="n">
+        <v>-0.7964</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/transocean-rig-soars-19-6-111319765.html</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Angelica Ballesteros</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2025-10-27T11:13:19Z</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Transocean (RIG) Soars 19.6% on Energy Boom</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>We recently published 10 of Wall Street’s Outperformers. Transocean Ltd. (NYSE:RIG) is one of the top-performing stocks last week. Transocean Ltd. jumped by ...</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>We recently published 10 of Wall Streets Outperformers. Transocean Ltd. (NYSE:RIG) is one of the top-performing stocks last week.
+Transocean Ltd. jumped by 19.63 percent week-on-week, as investor se… [+1855 chars]</t>
+        </is>
+      </c>
+      <c r="G494" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/iraq-negotiates-higher-opec-oil-103419952.html</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2025-10-27T10:34:19Z</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Iraq Negotiates Higher OPEC Oil Production Quota</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Iraq is negotiating with OPEC to raise its oil production quota as it boosts output capacity toward 5.5 million barrels per day and targets 6 million by 2029...</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Iraq is in discussions with OPEC to review its oil production quota as output capacity rises, Hayan Abdul Ghani, the Oil Minister of OPEC’s second largest producer, said on Monday. 
+Iraq is in talks… [+2458 chars]</t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/jeff-currie-sees-gold-bull-123507060.html</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2025-11-11T12:35:07Z</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Jeff Currie Sees Gold Bull Market Broadening Through Commodities</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Jeff Currie, chief strategy officer: energy pathways at Carlyle, says physical constraints are "biting" the commodity market. Currie also discusses US...</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Jeff Currie, chief strategy officer: energy pathways at Carlyle, says physical constraints are "biting" the commodity market. Currie also discusses US underinvestment in commodities and offers his ou… [+37 chars]</t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/asian-shares-mostly-lower-despite-060644238.html</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>CHAN HO-HIM</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2025-11-11T06:06:44Z</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Asian shares are mostly lower despite Wall St rally and a potential end to the US shutdown</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Asian shares were mostly lower on Tuesday as the recent rebound fueled by buying of technology shares lost steam.  U.S. futures were little changed and oil...</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>BANGKOK (AP) Asian shares were mostly lower on Tuesday as the recent rebound fueled by buying of technology shares lost steam.
+Markets showed little reaction to the latest step toward ending the U.S… [+3486 chars]</t>
+        </is>
+      </c>
+      <c r="G497" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-diverge-as-big-tech-wobbles-ahead-of-house-shutdown-vote-143510249.html</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2025-11-12T14:35:10Z</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq diverge as Big Tech wobbles ahead of House shutdown vote</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Investors awaited a key House vote that could end the longest government shutdown in US history.</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Oil prices fell on Wednesday as the Organization of Petroleum Exporting Countries (OPEC) left its global oil demand forecast unchanged from October in its monthly report and the International Energy … [+1768 chars]</t>
+        </is>
+      </c>
+      <c r="G498" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-rise-as-ai-hopes-swing-back-ahead-of-house-shutdown-vote-001226006.html</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2025-11-12T00:12:26Z</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as AI hopes swing back ahead of House shutdown vote</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Investors awaited a key House vote that could end the longest government shutdown in US history.</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Oil prices fell on Wednesday as the Organization of Petroleum Exporting Countries (OPEC) left its global oil demand forecast unchanged from October in its monthly report and the International Energy … [+1768 chars]</t>
+        </is>
+      </c>
+      <c r="G499" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/enbridge-approves-1-4-billion-201250014.html</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>By Amanda Stephenson</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2025-11-14T20:12:50Z</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Enbridge approves $1.4 billion project to boost Canadian oil flows to US</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>(Reuters) -Canadian pipeline operator Enbridge on Friday approved $1.4 billion in expansion projects for its Mainline and Flanagan South pipelines to the U.</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>By Amanda Stephenson
+(Reuters) -Canadian pipeline operator Enbridge on Friday approved $1.4 billion in expansion projects for its Mainline and Flanagan South pipelines to the U.S., which it stressed… [+2543 chars]</t>
+        </is>
+      </c>
+      <c r="G500" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/the-oil-glut-will-last-into-2026-heres-why-its-unclear-how-big-it-will-be-161521392.html</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Jake Conley</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2025-11-02T16:15:21Z</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>The oil glut will last into 2026. Here's why it's unclear how big it will be.</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>The world's oil supply is largely expected to enter an extreme glut in 2026. Just how big that overhang will be is complicated.</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Investors and analysts have spent much of the year embracing the view that the oil market, which has been in oversupply mode, is heading straight for a glut through 2026 and that glut could reach as … [+6725 chars]</t>
+        </is>
+      </c>
+      <c r="G501" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/russian-oil-company-lukoil-sell-092238887.html</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>DAVID McHUGH</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2025-10-28T09:22:38Z</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Russian oil company Lukoil to sell international assets in response to Trump sanctions</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Russian oil company Lukoil says it is selling its international assets in response to sanctions imposed by U.S. President Donald Trump that aim to push...</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>FRANKFURT, Germany (AP) Russian oil company Lukoil says it is selling its international assets in response to sanctions imposed by U.S. President Donald Trump that aim to push Russia to agree to a ce… [+2453 chars]</t>
+        </is>
+      </c>
+      <c r="G502" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-rise-us-china-011947296.html</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>By Sam Li and Lewis Jackson</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2025-10-27T01:19:47Z</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Oil prices rise after US and China reach trade-deal framework</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices rose in early trade on Monday after U. and Chinese economic officials sketched out a trade-deal framework, easing fears that tariffs...</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>By Sam Li and Lewis Jackson
+(Reuters) -Oil prices rose in early trade on Monday after U.S. and Chinese economic officials sketched out a trade-deal framework, easing fears that tariffs and export cu… [+1796 chars]</t>
+        </is>
+      </c>
+      <c r="G503" t="n">
+        <v>-0.1779</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/india-intensifying-search-oil-gas-080200173.html</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2025-10-27T08:02:00Z</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>India Is Intensifying Its Search for Oil and Gas as Import Pressure Builds</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>India is intensifying its search for domestic oil and gas discoveries to reduce heavy import dependence and achieve greater energy self-reliance.</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>India needs more local discoveries of oil and gas in order to be able to meet future energy demand, the secretary of petroleum and natural gas at the Indian energy ministry said.
+“One day, we will b… [+2295 chars]</t>
+        </is>
+      </c>
+      <c r="G504" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-edge-higher-opec-012200594.html</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2025-11-03T01:22:00Z</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Oil Prices Edge Higher After OPEC+ Pauses Output Hikes in Early 2026</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Oil prices rose slightly after OPEC+ announced a small December output hike and paused early-2026 increases, reflecting caution amid global demand and...</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Oil prices rose modestly in early Asian trading on Monday after OPEC+ opted for a limited production increase in December and delayed further hikes in the first quarter of 2026, signalling caution am… [+2112 chars]</t>
+        </is>
+      </c>
+      <c r="G505" t="n">
+        <v>-0.128</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/targa-resources-price-target-raised-134423673.html</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2025-11-07T13:44:23Z</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Targa Resources price target raised to $196 from $185 at BMO Capital</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>BMO Capital analyst Ameet Thakkar raised the firm’s price target on Targa Resources (TRGP) to $196 from $185 and keeps an Outperform rating on the shares...</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>BMO Capital analyst Ameet Thakkar raised the firms price target on Targa Resources (TRGP) to $196 from $185 and keeps an Outperform rating on the shares. The companys Q3 results demonstrate its resil… [+487 chars]</t>
+        </is>
+      </c>
+      <c r="G506" t="n">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/crescent-energy-crgy-rallies-5th-120113531.html</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Angelica Ballesteros</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2025-11-12T12:01:13Z</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Crescent Energy (CRGY) Rallies for 5th Day on Higher Oil, Gas Prices, Upcoming Dividend</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>We recently published 10 Stocks on a Hot Streak. Crescent Energy Company (NYSE:CRGY) is one of the best-performing stocks on Tuesday. Crescent Energy...</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>We recently published 10 Stocks on a Hot Streak. Crescent Energy Company (NYSE:CRGY) is one of the best-performing stocks on Tuesday.
+Crescent Energy extended its winning streak to a 5th straight da… [+1835 chars]</t>
+        </is>
+      </c>
+      <c r="G507" t="n">
+        <v>0.8625</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-falls-opec-output-plans-080702485.html</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>By Ashitha Shivaprasad and Sam Li</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2025-10-28T08:07:02Z</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Oil falls as OPEC+ output plans offset US-China trade optimism</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>By Ashitha Shivaprasad and Sam Li (Reuters) -Oil prices fell on Tuesday, marking their third day of declines as an OPEC+ plan to raise output outweighed...</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>By Ashitha Shivaprasad and Sam Li
+(Reuters) -Oil prices fell on Tuesday, marking their third day of declines as an OPEC+ plan to raise output outweighed optimism about a potential U.S.-China trade d… [+2234 chars]</t>
+        </is>
+      </c>
+      <c r="G508" t="n">
+        <v>0.7906</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-dips-opec-output-plans-014514374.html</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2025-10-28T01:45:14Z</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Oil dips as OPEC output plans offset US-China trade optimism</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>() -Oil prices slipped on Tuesday, extending falls from the two previous sessions, as pressure from plans by OPEC to boost output offset optimism over a...</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>(Reuters) -Oil prices slipped on Tuesday, extending falls from the two previous sessions, as pressure from plans by OPEC to boost output offset optimism over a potential U.S.-China trade deal.
+Brent… [+1864 chars]</t>
+        </is>
+      </c>
+      <c r="G509" t="n">
+        <v>0.8176</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exxonmobil-beats-q3-earnings-estimates-163800637.html</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Zacks Equity Research</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2025-10-31T16:38:00Z</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>ExxonMobil Beats Q3 Earnings Estimates, Boosts Dividend Again</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>XOM tops Q3 earnings estimates on higher production and gas prices, but revenue and oil realizations fall short.</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation XOM has reported third-quarter 2025 earnings per share of $1.88 (excluding identified items), which beat the Zacks Consensus Estimate of $1.81. The bottom line declined from t… [+7188 chars]</t>
+        </is>
+      </c>
+      <c r="G510" t="n">
+        <v>0.5423</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crude_oil_sentiment_score_.xlsx
+++ b/data/crude_oil_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G510"/>
+  <dimension ref="A1:G610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18547,6 +18547,3537 @@
         <v>0.5423</v>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tanker-seizure-forces-chevron-slash-230000627.html</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2025-12-15T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Tanker Seizure Forces Chevron to Slash Prices on Venezuelan Crude</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Chevron cut the price of Venezuelan crude after U.S. forces seized a tanker carrying sanctioned oil, adding pressure to an already weak Gulf Coast market.</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Chevron has quietly cut the price of Venezuelan crude sold to U.S. refiners after American forces seized a tanker off the country’s coast, tightening an already-fragile export channel and adding fres… [+3254 chars]</t>
+        </is>
+      </c>
+      <c r="G511" t="n">
+        <v>-0.891</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-oil-pumping-power-breaks-010000006.html</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2025-12-11T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>China’s Oil Pumping Power Breaks All Records</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>China has boosted domestic crude output from 3.8 million b/d in 2020 to 4.3 million b/d in 2025 — just as foreign investors find themselves locked out of the...</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>China is closing 2025 with the strongest domestic crude output in its modern history, ending its Seven-Year Action Plan (20192025) with measurable gains. National production has risen from 3.8 millio… [+8402 chars]</t>
+        </is>
+      </c>
+      <c r="G512" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/oil-prices-rise-4-low-153516400.html</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2025-12-17T15:35:16Z</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Oil prices rise after 4-year low: What Trump has to do with it</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Crude oil (CL=F, BZ=F) prices hit their lowest level since 2021 on Tuesday but have since rebounded during Wednesday's trading session. This comes as...</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Let's turn to the oil market because oil is rebounding after hitting its lowest level since 2021. Crude prices did drop below $55 a barrel on Tuesday. And this coming as President Trump is ordering a… [+4226 chars]</t>
+        </is>
+      </c>
+      <c r="G513" t="n">
+        <v>-0.8591</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/oil-declines-gold-soars-2025-183000919.html</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2025-12-22T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Oil declines, gold soars in 2025: Next phase in commodity super cycle</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Gold prices (GC=F) soared to a new record high above $4,400 per ounce on Monday — the precious metal is up over 70% year-to-date in 2025 — while crude oil...</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>You mentioned the commodities super cycle, and I know that includes some bullishness on oil, which is a little bit out of consensus, right? Um Jay, you know, I've seen some some estimates out there t… [+1853 chars]</t>
+        </is>
+      </c>
+      <c r="G514" t="n">
+        <v>0.8316</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/venezuelas-pdvsa-says-operations-unaffected-132124746.html</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2025-12-15T18:04:34Z</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Venezuela's PDVSA suffers cyberattack as tankers make u-turns</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Dec 15 (Reuters) - Venezuela's PDVSA was subject to a cyberattack that it blamed on the United States, the state-run oil company said on Monday, adding that ...</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Dec 15 (Reuters) - Venezuela's PDVSA was subject to a cyberattack that it blamed on the United States, the state-run oil company said on Monday, adding that its operations were unaffected even though… [+3398 chars]</t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>-0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-slip-as-unemployment-rate-rises-tesla-marches-toward-record-202215883.html</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Karen Friar</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2025-12-16T20:22:15Z</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500 slip as unemployment rate rises, Tesla marches toward record</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Investors reacted to the delayed release of the November jobs report, seen as pivotal to the path of interest rates next year.</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Crude oil prices fell to levels not seen since the doldrums of the pandemic at the start of 2021, as a widely expected supply glut picked up momentum and peace talks in the Russia-Ukraine conflict to… [+2184 chars]</t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>-0.6597</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-slip-nasdaq-gains-as-jobs-report-beats-estimates-unemployment-rate-rises-230828429.html</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Karen Friar</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2025-12-15T23:08:28Z</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500 slip, Nasdaq gains as jobs report beats estimates, unemployment rate rises</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Investors reacted to the delayed release of the November jobs report, seen as pivotal to the path of interest rates next year.</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Crude oil prices fell to levels not seen since the doldrums of the pandemic at the start of 2021, as a widely expected supply glut picked up momentum and peace talks in the Russia-Ukraine conflict to… [+2184 chars]</t>
+        </is>
+      </c>
+      <c r="G517" t="n">
+        <v>-0.4588</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-slip-nasdaq-snaps-three-day-losing-streak-as-tesla-climbs-to-record-210029709.html</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Karen Friar</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2025-12-16T21:03:25Z</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500 slip, Nasdaq snaps three-day losing streak as Tesla climbs to record</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Investors reacted to the delayed release of the November jobs report, seen as pivotal to the path of interest rates next year.</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Crude oil prices fell to levels not seen since the doldrums of the pandemic at the start of 2021, as a widely expected supply glut picked up momentum and peace talks in the Russia-Ukraine conflict to… [+2184 chars]</t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>-0.6249</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/3-high-yield-oil-stocks-154600772.html</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Nilanjan Choudhury</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2025-12-11T15:46:00Z</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>3 High-Yield Oil Stocks for Stable Income in a Bearish Market</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>CNQ, CVX and KMI offer yields over 4% and stable cash flow - key strengths in a bearish oil market heading into 2026.</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Oil markets are entering 2026 with rising inventories and weaker demand growth, creating a challenging backdrop for crude prices. Forecasts call for Brent and WTI to fall below $60 per barrel as a gl… [+5188 chars]</t>
+        </is>
+      </c>
+      <c r="G519" t="n">
+        <v>-0.128</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/trump-says-orders-blockade-sanctioned-011845545.html</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2025-12-17T01:18:45Z</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Trump says orders blockade of 'sanctioned' Venezuela oil tankers</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>US President Donald Trump announced Tuesday a blockade of "sanctioned oil vessels" heading to and leaving Venezuela, sharply escalating his pressure campaign...</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>US President Donald Trump announced Tuesday a blockade of "sanctioned oil vessels" heading to and leaving Venezuela, sharply escalating his pressure campaign against Caracas while issuing new demands… [+2698 chars]</t>
+        </is>
+      </c>
+      <c r="G520" t="n">
+        <v>-0.296</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bear-day-chevron-cvx-110900498.html</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Tracey Ryniec</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2025-11-26T11:09:00Z</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Bear of the Day: Chevron (CVX)</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Will oil turn around in 2026?</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Chevron Corp. CVX is waiting for a turnaround in oil prices. This Zacks Rank #5 (Strong Sell) is expected to see declining earnings for the second year in a row in 2025.
+Chevron is one of the worlds… [+2291 chars]</t>
+        </is>
+      </c>
+      <c r="G521" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/oil-blockade-threat-creates-anxiety-183206661.html</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>REGINA GARCIA CANO</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2025-12-17T18:32:06Z</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>The oil blockade threat creates anxiety in Venezuela but people stick to their daily lives</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>U.S. President Donald Trump is threating to blockade sanctioned oil tankers from Venezuela, a move that could devastate a country already wrangling with...</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>CARACAS, Venezuela (AP) U.S. President Donald Trump is threating to blockade sanctioned oil tankers from Venezuela, a move that could devastate a country already wrangling with years of spiraling cri… [+1811 chars]</t>
+        </is>
+      </c>
+      <c r="G522" t="n">
+        <v>-0.9127</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ukraine-strikes-key-russian-oil-122800963.html</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2025-12-11T12:28:00Z</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Ukraine Strikes Key Russian Oil Platform in Caspian Sea</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Ukraine's security services executed a long-range drone strike on Lukoil's Vladimir Filanovsky offshore oil field in the Caspian Sea, marking an...</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>In a significant expansion of its campaign against Russian energy infrastructure, Ukraines security services executed a long-range drone strike on a major offshore oil field in the Caspian Sea, effec… [+5430 chars]</t>
+        </is>
+      </c>
+      <c r="G523" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/federal-judge-blocks-whitmer-shutting-194405255.html</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>TODD RICHMOND</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2025-12-17T19:44:05Z</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Federal judge blocks Whitmer from shutting down submerged Great Lakes pipeline</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>A federal judge on Wednesday blocked Michigan Gov. Gretchen Whitmer 's attempt to shut down an aging oil pipeline running beneath a channel linking two of...</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>A federal judge on Wednesday blocked Michigan Gov. Gretchen Whitmer 's attempt to shut down an aging oil pipeline running beneath a channel linking two of the Great Lakes, finding that only the feder… [+3484 chars]</t>
+        </is>
+      </c>
+      <c r="G524" t="n">
+        <v>0.7351</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-seized-tanker-near-venezuela-024355079.html</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>By Jasper Ward</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2025-12-13T02:43:55Z</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>US seized tanker near Venezuela just as warrant was set to expire, court document shows</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>By Jasper Ward WASHINGTON, Dec 12 (Reuters) - The U.S. government carried out its seizure of the M/T Skipper off the coast of Venezuela on Wednesday just as ...</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>By Jasper Ward
+WASHINGTON, Dec 12 (Reuters) - The U.S. government carried out its seizure of the M/T Skipper off the coast of Venezuela on Wednesday just as a judge-signed warrant was set to expire,… [+1622 chars]</t>
+        </is>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-vaults-toward-record-high-as-oracles-slide-weighs-on-sp-500-nasdaq-233526728.html</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2025-12-10T23:35:26Z</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow vaults toward record high as Oracle's slide weighs on S&amp;P 500, Nasdaq</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Oracle's revenue miss is reviving the AI bubble debate, dampening spirits on Wall Street.</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>The Dow surged toward a record on Thursday as US stocks diverged, with more tech-exposed gauges under pressure after Oracle (ORCL) earnings revived AI overspending worries.
+The Nasdaq Composite (^IX… [+15496 chars]</t>
+        </is>
+      </c>
+      <c r="G526" t="n">
+        <v>-0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>https://uk.finance.yahoo.com/news/oil-prices-russia-ukraine-peace-talks-gold-pound-094824291.html</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Vicky McKeever</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2025-11-28T09:48:24Z</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Oil prices rise as investors eye developments on Russia-Ukraine talks</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Oil prices rose on Friday morning, as Vladimir Putin said a draft of US-Ukraine proposals could form the basis of a future peace deal.</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Oil prices rose on Friday morning, as investors weighed developments on Russia-Ukraine peace talks.
+Brent crude (BZ=F) futures climbed 0.5% to $62.47 per barrel at the time of writing, while West Te… [+3726 chars]</t>
+        </is>
+      </c>
+      <c r="G527" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-readies-russia-sanctions-putin-100442703.html</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Eric Martin, Kate Sullivan, Alberto Nardelli and Natalia Drozdiak</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2025-12-17T10:04:42Z</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>US Readies New Russia Sanctions If Putin Rejects Peace Deal</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>The US is considering options, such as targeting vessels in Russia’s so-called shadow fleet of tankers used to transport Moscow’s oil, as well as traders who...</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- The US is preparing a fresh round of sanctions on Russias energy sector to increase the pressure on Moscow should President Vladimir Putin reject a peace agreement with Ukraine, accord… [+5356 chars]</t>
+        </is>
+      </c>
+      <c r="G528" t="n">
+        <v>0.8316</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exclusive-nigerias-dangote-picks-honeywell-033342515.html</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>By Utkarsh Shetti</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2025-11-25T03:33:42Z</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Exclusive-Nigeria's Dangote picks Honeywell to help fulfill ambitious capacity expansion</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>DUBAI (Reuters) -Nigeria's Dangote has tapped Honeywell to provide services and help double its refining capacity to 1.4 million ​barrels per day by 2028, in...</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>By Utkarsh Shetti
+DUBAI (Reuters) -Nigeria's Dangote has tapped Honeywell to provide services and help double its refining capacity to 1.4 million barrels per day by 2028, in what is the clearest in… [+1887 chars]</t>
+        </is>
+      </c>
+      <c r="G529" t="n">
+        <v>0.886</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/3-oil-pipeline-stocks-solid-131200974.html</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Nilanjan Banerjee</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2025-12-09T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>3 Oil Pipeline Stocks With Solid Potential Amid Industry Strength</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Midstream players will secure additional cashflows from rising clean energy demand from data centers, which brightens the outlook for the Zacks Oil and Gas -...</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Unlike the upstream players, the business model of midstream companies is less vulnerable to the volatility in oil and natural gas prices. Importantly, rising clean energy demand from the data center… [+6313 chars]</t>
+        </is>
+      </c>
+      <c r="G530" t="n">
+        <v>0.8832</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-jumps-650-points-to-post-record-sp-500-climbs-above-6900-for-first-time-210051184.html</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2025-12-11T21:00:51Z</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow jumps X post to record, S&amp;P 500 climbs above 6,900 for first time</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>The Dow and S&amp;P 500 notched new records on Thursday as US stocks mostly rose, with tech stocks under more pressure after Oracle (ORCL) earnings revived AI...</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>The Dow and S&amp;amp;P 500 notched new records on Thursday as US stocks mostly rose, with tech stocks under more pressure after Oracle (ORCL) earnings revived AI overspending worries.
+The Dow Jones Ind… [+15789 chars]</t>
+        </is>
+      </c>
+      <c r="G531" t="n">
+        <v>-0.6478</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>https://uk.finance.yahoo.com/news/gold-price-oil-gold-interest-rates-dollar-103833596.html</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Pedro Goncalves</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2025-12-08T10:38:33Z</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Gold back above $4,200 as Fed cut bets rise</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>The weak dollar supported demand for bullion, as it makes gold cheaper for overseas buyers.</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Gold prices were mixed on Monday morning but were back above the $4,200 level as expectations of a US interest rate cut weighed on the dollar ahead of this weeks Federal Reserve policy meeting.
+Gold… [+4248 chars]</t>
+        </is>
+      </c>
+      <c r="G532" t="n">
+        <v>0.2023</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/dow-sp-500-nasdaq-futures-hit-pause-on-rally-before-cme-glitch-halts-trading-000737072.html</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2025-11-28T00:07:37Z</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Dow, S&amp;P 500, Nasdaq futures climb although gauges are on track to end month in the red</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Trading in stock futures has been disrupted by a CME outage ahead of a holiday-shortened session.</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>US stock futures were muted heading into the end of a holiday-shortened week, before the Chicago Mercantile Exchange halted trading on Friday due to a data center glitch.
+The ongoing CME outage has … [+1741 chars]</t>
+        </is>
+      </c>
+      <c r="G533" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-military-says-strikes-3-025351944.html</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>The Associated Press</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2025-12-16T02:53:51Z</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>US military says strikes on 3 boats in the eastern Pacific Ocean kill 8 people</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>The U.S. military said Monday that it attacked three boats accused of smuggling drugs in the eastern Pacific Ocean, killing a total of eight people as...</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>WASHINGTON (AP) The U.S. military said Monday that it attacked three boats accused of smuggling drugs in the eastern Pacific Ocean, killing a total of eight people as scrutiny over the boat strikes i… [+1869 chars]</t>
+        </is>
+      </c>
+      <c r="G534" t="n">
+        <v>-0.9698</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-sp-500-dow-rise-to-end-a-rocky-month-nasdaq-snaps-7-month-win-streak-180355656.html</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2025-11-28T18:03:55Z</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Stock market today: S&amp;P 500, Dow rise to end a rocky month, Nasdaq snaps 7-month win streak</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>US stocks rose for the fifth day in a row on Friday, but the Nasdaq snapped its monthly winning streak.</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>US stocks rose during a holiday-shortened trading day on Friday as a volatile month drew to a close and the Nasdaq Composite (^IXIC) snapped a seven-month win streak.
+The tech-heavy Nasdaq Composite… [+11000 chars]</t>
+        </is>
+      </c>
+      <c r="G535" t="n">
+        <v>0.8225</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/dow-sp-500-nasdaq-futures-muted-as-rocky-month-draws-to-an-end-before-cme-glitch-halts-trading-000737050.html</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2025-11-28T00:07:37Z</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Dow, S&amp;P 500, Nasdaq futures muted as rocky month draws to an end, before CME glitch halts trading</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>CME is gradually resuming operations after a futures outage that halted trading in US stock indexes.</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>US stock futures were muted with a holiday-shortened week and downbeat month drawing to an end, before the Chicago Mercantile Exchange halted trading on Friday due to a data center glitch.
+The CME i… [+3380 chars]</t>
+        </is>
+      </c>
+      <c r="G536" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/saudi-arabia-quietly-expands-access-061328942.html</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>BARAA ANWER</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2025-12-21T06:13:28Z</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Saudi Arabia quietly expands access to its only alcohol store for non-Muslim residents</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Saudi Arabia has quietly expanded access to its only store that sells alcohol, allowing wealthy foreign residents to buy booze in the latest step in the once...</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>RIYADH, Saudi Arabia (AP) Saudi Arabia has quietly expanded access to its only store that sells alcohol, allowing wealthy foreign residents to buy booze in the latest step in the once-ultraconservati… [+3275 chars]</t>
+        </is>
+      </c>
+      <c r="G537" t="n">
+        <v>0.4404</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/admiral-hands-over-leadership-command-165048404.html</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>JOSHUA GOODMAN</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2025-12-12T16:50:48Z</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Admiral hands over leadership of command overseeing the Trump administration's boat strikes</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>A U.S. Navy admiral who oversees military operations in Latin America handed off command responsibilities Friday as scrutiny increases over the Trump...</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>DORAL, Fla. (AP) A U.S. Navy admiral who oversees military operations in Latin America handed off command responsibilities Friday as scrutiny increases over the Trump administration's deadly strikes … [+4380 chars]</t>
+        </is>
+      </c>
+      <c r="G538" t="n">
+        <v>-0.1027</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-fall-as-netflix-skids-on-deal-drama-nvidia-rises-205106952.html</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2025-12-08T20:51:06Z</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq fall as Netflix skids on merger drama, Nvidia rises</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>US stocks fell ahead of the Federal Reserve's mid-week announcement on interest rates.</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>US stocks fell on Monday as Wall Street awaits the Federal Reserve's final policy meeting of the year, while the deal drama between Netflix (NFLX) and Warner Bros. Discovery (WBD) escalated to a new … [+9705 chars]</t>
+        </is>
+      </c>
+      <c r="G539" t="n">
+        <v>0.0772</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-steady-with-wall-street-awaiting-expected-fed-rate-cut-001431798.html</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2025-12-08T00:14:31Z</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq with Wall Street awaiting expected Fed rate cut</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>US stock futures were steady ahead of the Federal Reserve's mid-week announcement on interest rates.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>US stocks stalled on Monday, as Wall Street headed into a pivotal week dominated by the Federal Reserve's final policy meeting of 2025.
+The tech-heavy Nasdaq Composite (^IXIC) rose roughly 0.2%, whi… [+7843 chars]</t>
+        </is>
+      </c>
+      <c r="G540" t="n">
+        <v>-0.4404</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/texas-producer-battles-california-restart-220000756.html</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2025-11-30T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Texas Producer Battles California to Restart Offshore Oil Platforms</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>A Texas oil firm is fighting an uphill battle with the state of California to restart crude oil production and sales from three platforms in federal waters...</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>A Texas oil firm is fighting an uphill battle with the state of California to restart crude oil production and sales from three platforms in federal waters offshore Santa Barbara.
+Houston-based Sabl… [+5797 chars]</t>
+        </is>
+      </c>
+      <c r="G541" t="n">
+        <v>-0.886</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-tanker-rates-skyrocket-467-110000581.html</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2025-12-11T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Oil Tanker Rates Skyrocket 467%</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>A shortage of supertankers is tightening the market and causing oil tanker charter rates to surge by 467% as new vessels race empty to load crude amid rising...</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>The supertanker market has tightened this year as crude supply from OPEC+ and the Americas rises and vessels make increasingly longer trips. So much has the market tightened that several new-built ve… [+2513 chars]</t>
+        </is>
+      </c>
+      <c r="G542" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/real-reason-behind-u-resuming-170000429.html</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Simon Watkins</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2025-12-15T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>The Real Reason Behind U.S. Resuming Iraqi Kurdistan Oil Imports</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>U.S. imports of Kurdish crude are less about oil and more about geopolitics.</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>An oil tanker carrying crude from the Kurdistan Region of Iraq (KRI) unloaded its cargo at a U.S. port at the very end of last month – the first since the reopening of the critical Iraq-Turkey Pipeli… [+8700 chars]</t>
+        </is>
+      </c>
+      <c r="G543" t="n">
+        <v>-0.7184</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venezuela-oil-future-hinges-u-000000970.html</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2025-12-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Venezuela’s Oil Future Hinges on U.S. Tensions and Possible Regime Shift</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Regime change in Venezuela could reshape global oil flows, giving the U.S. renewed access to heavy crude.</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Escalating tensions between the United States and Venezuela could lead to profound changes in the oil industry of the world’s largest crude resource holder.
+Any regime change of President Nicolas Ma… [+5095 chars]</t>
+        </is>
+      </c>
+      <c r="G544" t="n">
+        <v>-0.743</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_772a6552-8923-452c-8305-ae3bb6b2809f</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2025-12-17T08:59:53Z</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Is Crude Oil a Good Investment for 2026?</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 242 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G545" t="n">
+        <v>0.4019</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_f5cb8526-dc9a-4bf8-97f3-d2858ad92bed</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2025-12-17T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Venezuela’s Falling Crude Supply Won’t Budge Global Oil Market</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 242 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G546" t="n">
+        <v>-0.2023</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chevron-ships-venezuelan-crude-despite-213833702.html</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2025-12-18T21:38:33Z</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Chevron Ships Venezuelan Crude Despite Rising U.S. Pressure</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Chevron Corp. is preparing to export up to 1 million barrels of crude from Venezuela, even as U.S. pressure on the country’s oil trade intensifies following ...</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Chevron Corp. is preparing to export up to 1 million barrels of crude from Venezuela, even as U.S. pressure on the country’s oil trade intensifies following fresh accusations from President Donald Tr… [+2610 chars]</t>
+        </is>
+      </c>
+      <c r="G547" t="n">
+        <v>-0.8277</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-markets-lackluster-amid-russia-230000354.html</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2025-11-27T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Oil Markets Lackluster Amid Russia Peace Deal, China’s Stockpiling</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>China continues aggressive stockpiling, importing over 11.4 mb/d of crude and adding roughly 1 mb/d to reserves in some months.</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Sentiment in oil markets remains overwhelmingly negative, driven by perceived market oversupply and negative global demand indicators. Brent crude for January delivery was trading at $63.10 per barre… [+5417 chars]</t>
+        </is>
+      </c>
+      <c r="G548" t="n">
+        <v>-0.8625</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/russia-looks-ramp-crude-flows-062900046.html</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2025-11-25T06:29:00Z</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Russia Looks to Ramp Up Crude Flows to China Through 2033</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Russia is seeking to extend and expand crude oil exports to China through both seaborne and pipeline routes as its energy revenues decline under sanctions...</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Russia could boost its crude oil exports to China, extending existing agreements, Deputy Prime Minister Alexander Novak said today, noting specifically a deal for the export of Russian crude via Kaza… [+2343 chars]</t>
+        </is>
+      </c>
+      <c r="G549" t="n">
+        <v>-0.8074</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/invested-10k-exxon-mobil-stock-130143238.html</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>David Kirakosyan</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2025-11-29T13:01:43Z</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>If You Invested $10K In Exxon Mobil Stock 10 Years Ago, How Much Would You Have Now?</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corp. (NYSE:XOM) is a global energy and chemical company that explores for, produces, and sells crude oil and natural gas. It is set to report...</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Benzinga and Yahoo Finance LLC may earn commission or revenue on some items through the links below.
+Exxon Mobil Corp. (NYSE:XOM) is a global energy and chemical company that explores for, produces,… [+2335 chars]</t>
+        </is>
+      </c>
+      <c r="G550" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/canadas-third-quarter-annualized-gdp-150419986.html</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>By Promit Mukherjee</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2025-11-28T15:04:19Z</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Canada's third-quarter annualized GDP surprises with growth of 2.6%</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>OTTAWA (Reuters) -Canada's economy grew at a much faster pace than expected in the third quarter as crude oil exports and government spending boosted...</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>By Promit Mukherjee
+OTTAWA (Reuters) -Canada's economy grew at a much faster pace than expected in the third quarter as crude oil exports and government spending boosted economic activity, data show… [+2390 chars]</t>
+        </is>
+      </c>
+      <c r="G551" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-trump-tariffs-hurt-drillers-150000712.html</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Robert Rapier</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2025-11-25T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Why Trump’s Tariffs Hurt Drillers More Than Refiners</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Trump’s second-term tariff strategy shields crude imports while driving up steel and equipment costs across the oil and gas value chain, reshaping project...</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>President Trump’s tariff strategy in his second term has touched almost every corner of the economy, but few sectors have felt the effects as unevenly as oil and gas. The administration has chosen no… [+7165 chars]</t>
+        </is>
+      </c>
+      <c r="G552" t="n">
+        <v>-0.296</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-upends-weak-oil-demand-220000689.html</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2025-12-14T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>China Upends the Weak Oil-Demand Narrative</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>With China seen ramping up the rate at which it puts oil into storage, the price stability will likely remain a feature of oil markets in 2026,</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>China’s latest oil import data has been rather bullish, with November imports rising 5% year on year. Not only that, but China is building new storage capacity, so it can keep buying more crude, inst… [+5415 chars]</t>
+        </is>
+      </c>
+      <c r="G553" t="n">
+        <v>-0.8146</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/india-signals-50-cut-russian-093044306.html</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2025-12-01T09:30:44Z</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>India Signals a 50% Cut in Russian Oil Imports Under U.S. Sanctions Pressure</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>India is preparing to cut Russian crude imports by about 50% as U.S. sanctions push refiners and banks to scale back purchases despite a final pre-deadline...</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>India could reduce its imports of Russian crude oil by 50%, a former foreign minister in New Delhi told local media, noting that both India and Russia would nevertheless look for ways to go around U.… [+2328 chars]</t>
+        </is>
+      </c>
+      <c r="G554" t="n">
+        <v>-0.7906</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-steadies-two-day-drop-103247112.html</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Yongchang Chin</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2025-12-10T10:32:47Z</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Oil Steadies After Two-Day Drop With Glut Concerns to the Fore</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Brent crude traded around $62 a barrel after losing 3% over the previous two sessions, while West Texas Intermediate was above $58.  The US said domestic...</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Photographer: Matthew Busch/Bloomberg
+(Bloomberg) -- Oil held the biggest two-day drop in a month as concerns about global oversupply continued to weigh on sentiment.
+Brent crude traded around $62 … [+1507 chars]</t>
+        </is>
+      </c>
+      <c r="G555" t="n">
+        <v>-0.7845</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-climbs-opec-reiterates-pause-005014636.html</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Alex Longley and Will Kubzansky</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2025-12-01T16:21:39Z</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Oil Gains With Attack on Key Black Sea Terminal, Venezuela Risk</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>West Texas Intermediate traded above $59 on Monday and earlier rose as much as 2.4%.  The Caspian Pipeline Consortium carries most of Kazakhstan’s crude...</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Oil rose as a key pipeline linking Kazakh fields to Russias Black Sea coast halted loading after one of its three moorings was damaged amid Ukrainian attacks in the region over the wee… [+2386 chars]</t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>-0.8225</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/saudi-arabia-set-slash-oil-120000300.html</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2025-11-28T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Set to Slash Oil Prices to Asia for January</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Saudi Aramco is expected to cut January crude prices for Asia to the lowest premium since 2021 amid ample supply and weakening Middle East benchmarks.</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Saudi Arabia is expected to slash the prices for its crude bound for Asia in January to the lowest premium to benchmarks in five years, as the world’s largest crude exporter looks to preserve market … [+2497 chars]</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>-0.9217</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-fall-to-4-year-low-below-55-as-supply-glut-shows-up-163301947.html</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Jake Conley</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2025-12-16T16:33:01Z</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Oil prices fall to 4-year low below $55 as supply glut shows up</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Oil prices spiraled downward on Tuesday as the coming oversupply wave picked up momentum.</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Crude oil prices fell to levels not seen since the start of 2021 as a widely expected supply glut picked up momentum and peace talks in the Russia-Ukraine conflict took steps forward.
+Futures on int… [+6231 chars]</t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>-0.5574</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-slip-peace-deal-020700220.html</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2025-11-27T02:07:00Z</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Oil Prices Slip on Peace Deal Progress</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Oil prices slipped on renewed Russia-Ukraine peace optimism and uncertainty ahead of Sunday’s OPEC+ meeting, with markets increasingly focused on oversupply ...</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Oil prices slipped in early Asian trade on Thursday as markets digested renewed hope for a Russia-Ukraine peace deal and braced for a key OPEC+ meeting scheduled to take place on Sunday.
+At the time… [+2216 chars]</t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>0.9136</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/murban-growing-market-depth-puts-010000507.html</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2025-12-04T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Murban’s Growing Market Depth Puts It Head-to-Head With WTI in Asia</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Murban crude has evolved from a supplemental grade in the Dubai basket into a major global benchmark.</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Back in 2016, Murban crude was introduced into the Dubai basket, along with Al-Shaheen, as a response to a lack of supply and price volatility caused by limited physical crude availability for the be… [+5533 chars]</t>
+        </is>
+      </c>
+      <c r="G560" t="n">
+        <v>-0.872</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-headed-fourth-monthly-114500054.html</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2025-11-28T11:45:00Z</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Oil Prices Headed for Fourth Monthly Loss as Glitch Halts Trading</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>A data center outage at CME halted global futures trading as oil prices headed for a fourth straight monthly loss amid oversupply concerns and geopolitical...</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Oil prices were headed for a fourth consecutive monthly loss early on Friday as a data center glitch forced CME Group to halt trading in futures and options, disrupting oil futures trades as well as … [+2236 chars]</t>
+        </is>
+      </c>
+      <c r="G561" t="n">
+        <v>-0.6705</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-venezuela-campaign-disrupts-8-220000023.html</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2025-12-21T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Trump’s Venezuela Campaign Disrupts an $8 Billion Oil Trade</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>The clampdown threatens up to $8 billion in oil revenues, as sanctioned “shadow fleet” vessels struggle to operate under heightened U.S. naval presence.</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Oil tankers are diverting from their route to Venezuela; some are sitting idle at ports instead of setting off for Asia; discounts on Venezuelan crude are deepening; and PDVSA may soon start shutting… [+5644 chars]</t>
+        </is>
+      </c>
+      <c r="G562" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-advances-us-pursues-third-043138265.html</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Bloomberg News</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2025-12-22T04:31:38Z</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Oil Advances as US Pursues Third Tanker in Venezuela Blockade</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Brent climbed to around $61 a barrel, after two weekly declines, while West Texas Intermediate was near $57.  The US Coast Guard boarded the Centuries tanker...</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>(Bloomberg) Oil rose as President Donald Trump intensified a blockade on Venezuela, with US forces boarding one tanker and pursuing another within weeks of first capturing a vessel.
+Brent (BZ=F) cli… [+1722 chars]</t>
+        </is>
+      </c>
+      <c r="G563" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-holds-biggest-decline-three-063226105.html</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Yongchang Chin and Alex Longley</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2025-12-09T09:54:42Z</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Oil Holds Biggest Decline in Three Weeks With Glut in Focus</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>The Energy Information Administration is set to release its Short-Term Energy Outlook on Tuesday, with reports due from the International Energy Agency and...</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Oil steadied after the biggest drop this month as traders look to reports coming this week to assess the extent of an oversupply.
+Brent crude traded held above $62 a barrel after tumb… [+944 chars]</t>
+        </is>
+      </c>
+      <c r="G564" t="n">
+        <v>-0.7003</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-ticks-higher-better-china-070034350.html</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Bloomberg News</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2025-12-15T16:55:46Z</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Oil Falls as Traders Weigh Ukraine Deal and China Outlook</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>West Texas Intermediate was below $57 a barrel in thin trading ahead of the Christmas and New Year holidays, sliding as stocks wavered.  Monday’s talks...</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Oil fell to the lowest level in almost two months, with traders weighing renewed signs of optimism surrounding a deal to end the war in Ukraine and mixed economic data from China.
+Wes… [+1917 chars]</t>
+        </is>
+      </c>
+      <c r="G565" t="n">
+        <v>-0.4588</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-executives-brace-another-tough-010000212.html</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2025-12-19T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Oil Executives Brace For Another Tough Year Ahead</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Oil executives expect oil markets to remain depressed, with respondents projecting West Texas Intermediate (WTI) oil prices to finish 2026 at $62 per barrel</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>The oil markets are looking to finish the year on the back foot, with oil prices falling again amid expectations of a supply glut and Russia-Ukraine peace talks reviving. Nearly half of oil executive… [+5702 chars]</t>
+        </is>
+      </c>
+      <c r="G566" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/canadian-energy-companies-outperforming-despite-000000108.html</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2025-12-01T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Canadian Energy Companies Are Outperforming Despite Weak Oil Prices</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Canadian energy stocks are surging, with the TSX Energy Index up 19.5% YTD vs. 6% for the S&amp;P Energy Index</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Recently, we have noted that U.S. investors are increasingly buying Canadian Oil &amp;amp; Gas companies, even as global oil prices move lower. According to McCrea, U.S. funds now own about 59% of Canadi… [+8104 chars]</t>
+        </is>
+      </c>
+      <c r="G567" t="n">
+        <v>0.3195</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-rise-opec-holds-022936126.html</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2025-12-01T02:29:36Z</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Oil Prices Rise as OPEC+ Holds Firm on Output Through Q1 2026</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Oil prices rose modestly after OPEC+ decided to maintain current production levels through early 2026, easing fears of a deeper supply glut.</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Oil prices rebounded in early Asian trade on Monday following the latest OPEC+ meeting, as traders responded to the producer group’s decision to hold output steady through the first quarter of 2026.
+… [+1764 chars]</t>
+        </is>
+      </c>
+      <c r="G568" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-expected-to-fall-in-2026-as-wall-street-sees-punishing-oversupply-risking-return-to-covid-levels-134609564.html</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Jake Conley</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2025-11-28T13:46:09Z</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Oil prices expected to fall in 2026 as Wall Street sees 'punishing oversupply' risking return to COVID levels</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Wall Street's biggest banks see oil prices falling into the $50s or lower per barrel in 2026 and beyond, teeing up a tough year for the oil and gas industry.</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Commodities strategists at Wall Street's top investment banks expect 2026 and 2027 to be tough years for the oil industry. And that's after a nearly 20% decline in oil prices this year.
+Under a base… [+5004 chars]</t>
+        </is>
+      </c>
+      <c r="G569" t="n">
+        <v>-0.6808</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-slips-as-jpmorgan-slides-sp-500-nasdaq-little-changed-with-all-eyes-on-fed-decision-210044915.html</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2025-12-09T21:00:44Z</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow slips as JPMorgan slides, S&amp;P 500, Nasdaq little changed with all eyes on Fed decision</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Wall Street is looking to the Fed policy meeting starting today for clues to the odds of more rate cuts in 2026.</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Exxon Mobil (XOM) shares rose by more than 2% after the company healthily raised its earnings and cash flow growth targets under a new 2030 corporate strategy released Tuesday.
+The oil supermajor, t… [+2236 chars]</t>
+        </is>
+      </c>
+      <c r="G570" t="n">
+        <v>0.5859</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/kosmos-energy-kos-misses-q3-164950262.html</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2025-12-09T16:49:50Z</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Kosmos Energy (KOS) Misses Q3 Estimates, Analysts Split on Outlook</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Kosmos Energy Ltd. (NYSE:KOS) is one of the cheap oil stocks under $10 to buy now. On December 5, Bank of America Securities analyst Matthew Smith cut his...</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Kosmos Energy Ltd. (NYSE:KOS) is one of the cheap oil stocks under $10 to buy now. On December 5, Bank of America Securities analyst Matthew Smith cut his rating on Kosmos Energy Ltd. (NYSE:KOS) to S… [+2181 chars]</t>
+        </is>
+      </c>
+      <c r="G571" t="n">
+        <v>0.5423</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/indonesia-invites-firms-explore-108-163000684.html</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2025-11-25T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Indonesia Invites Firms to Explore 108 Untapped Oil and Gas Basins</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Indonesia is inviting global investors to explore 108 previously untapped oil and gas basins as part of its strategy to reverse a production decline and...</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Indonesia looks to unlock its upstream potential by offering more than 100 previously untapped oil and gas basins to global investors for exploration.
+Southeast Asia’s biggest economy, which is also… [+2393 chars]</t>
+        </is>
+      </c>
+      <c r="G572" t="n">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gasoline-drops-below-3-half-230000563.html</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2025-11-26T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Gasoline Drops Below $3 in Half the U.S</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>A 17% year-to-date decline in oil prices, cheaper winter fuel blends, and lower post-Thanksgiving demand are combining to push pump prices down</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Drivers in half of U.S. states are enjoying average gasoline prices below $3 per gallon this Thanksgiving holiday, and prices at the pump are set to further decline going into Christmas.
+Lower crude… [+4203 chars]</t>
+        </is>
+      </c>
+      <c r="G573" t="n">
+        <v>0.5994</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/u-shale-starts-crack-under-210000901.html</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2025-11-26T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>U.S. Shale Starts to Crack Under $50–$60 Oil</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>With oil trading near $55–60 per barrel, many producers—especially smaller independents—are struggling to maintain profitability.</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Shale drillers are finding new and exciting ways to boost production in the Permian and elsewhere. This can make the industry more resilient to international price swings—but never fully resilient an… [+5491 chars]</t>
+        </is>
+      </c>
+      <c r="G574" t="n">
+        <v>0.7096</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-futures-tick-up-as-nvidia-jumps-ahead-of-fed-meeting-kickoff-233039719.html</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2025-12-08T23:30:39Z</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures tick up as Nvidia jumps ahead of Fed meeting kickoff</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>US stock futures inched up as Nvidia and the Fed dominate headlines in a busy week.</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Natural gas (NG=F) prices spent Monday in free fall, tumbling by more than 7.9% to drop back below the $5 mark.
+After a cold shock last week that saw prices jump above $5, a mark not seen since Dece… [+1487 chars]</t>
+        </is>
+      </c>
+      <c r="G575" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-holds-gains-natural-gas-160000619.html</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2025-11-28T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Oil Holds Gains, Natural Gas Rockets as OPEC+ Meeting Nears</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>As Russia-Ukraine peace talks drag on, dampening last week’s hopes that a swift resolution could be around the corner, ICE Brent has settled comfortably...</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Crude oil is holding gains ahead of Sunday's OPEC+ meeting, while U.S. natural gas prices have spiked on the news of a new U.S. LNG export record.
+Friday, November 28, 2025
+As Russia-Ukraine peace … [+5215 chars]</t>
+        </is>
+      </c>
+      <c r="G576" t="n">
+        <v>0.8225</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/hedge-funds-position-price-crash-150645419.html</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2025-12-09T15:06:45Z</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Hedge Funds Position for a Price Crash as Brent Shorts Hit All-Time High</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Oil prices continue to search for direction as a supply scare from Iraq turned out to be short-lived, with most market speculation centred around Ukraine...</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Is Now the Right Time to Finally Go Short on Oil Futures?
+- Behind the façade of calm oil markets, a gradual build-up in speculative positions could be undermining future prices of Brent or WTI as b… [+7212 chars]</t>
+        </is>
+      </c>
+      <c r="G577" t="n">
+        <v>-0.3612</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/vista-energy-moves-scale-vaca-185935755.html</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2025-12-17T18:59:35Z</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Vista Energy Moves to Scale Up Vaca Muerta Footprint</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Vista Energy SAB, one of Argentina’s leading shale oil producers, is preparing for a new phase of expansion in the Vaca Muerta formation and is weighing...</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Vista Energy SAB, one of Argentina’s leading shale oil producers, is preparing for a new phase of expansion in the Vaca Muerta formation and is weighing potential asset acquisitions that could be fin… [+2794 chars]</t>
+        </is>
+      </c>
+      <c r="G578" t="n">
+        <v>0.6908</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-rises-lowest-since-october-074825344.html</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Nicholas Lua and Alex Longley</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2025-12-12T13:53:23Z</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Oil Holds Near Lowest Since October With Surplus in Focus</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Global stock gauges have record highs in their sights as the Federal Reserve’s interest-rate cut this week and its upbeat assessment of the US economy...</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Bloomberg
+(Bloomberg) -- Oil held near its lowest close in almost two months, as concerns about an oversupply offset bullishness in wider financial markets.
+Brent traded little changed above $61, r… [+1561 chars]</t>
+        </is>
+      </c>
+      <c r="G579" t="n">
+        <v>-0.6369</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/propetro-holding-pump-slumps-following-114657008.html</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2025-12-20T11:46:57Z</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>ProPetro Holding (PUMP) Slumps Following Decline in Oil Price</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>The share price of ProPetro Holding Corp. (NYSE:PUMP) fell by 20% between December 10 and December 17, 2025, putting it among the Energy Stocks that Lost the...</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>The share price of ProPetro Holding Corp. (NYSE:PUMP) fell by 20% between December 10 and December 17, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+ProPetro Holding (PUMP) … [+1724 chars]</t>
+        </is>
+      </c>
+      <c r="G580" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/middle-east-crude-prices-sink-120000647.html</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2025-12-15T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Middle East Crude Prices Sink to Two-Month Low Against Brent</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Key crude prices in the Middle East have dropped to their weakest level against the Brent benchmark in two months, signaling an oversupplied market due to...</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Key crude prices in the Middle East have dropped to their weakest level against the Brent benchmark in two months, signaling oversupplied markets as output from both the Middle East and the Americas … [+2297 chars]</t>
+        </is>
+      </c>
+      <c r="G581" t="n">
+        <v>-0.9153</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ubs-cautious-conocophillips-cop-amid-130708132.html</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2025-11-25T13:07:08Z</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>UBS Cautious on ConocoPhillips (COP) Amid Increased Willow Project Cost Estimates, Maintains ‘Buy’ Rating</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is one of the most undervalued NYSE stocks to buy right now. On November 12, UBS lowered the firm’s price target on ConocoPhillips ...</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is one of the most undervalued NYSE stocks to buy right now. On November 12, UBS lowered the firms price target on ConocoPhillips to $117 from $122 and kept a Buy rating on … [+1738 chars]</t>
+        </is>
+      </c>
+      <c r="G582" t="n">
+        <v>0.0516</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/far-brent-wti-fall-oversupplied-000000733.html</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2025-12-18T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>How Far Can Brent and WTI Fall in an Oversupplied Market?</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Markets are pricing in a glut rather than disruption, as Russian exports remain steady and analysts broadly expect lower prices through 2026.</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Earlier this week, Brent crude slipped below $60 per barrel, and West Texas Intermediate dipped to $55, under the combined weight of a projected supply overhang and media reports claiming the United … [+5574 chars]</t>
+        </is>
+      </c>
+      <c r="G583" t="n">
+        <v>-0.2263</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-sinks-despite-rate-cuts-153000094.html</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2025-12-12T15:30:00Z</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Oil Sinks Despite Rate Cuts and Tanker Seizures</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Oil sentiment has turned sour despite a Fed rate cut and the Trump administration’s aggressive tanker seizures.</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Oil sentiment has turned sour despite a Fed rate cut and the Trump administrations aggressive tanker seizures.
+Friday, December 12, 2025 
+The US Federal Reserve has lowered the federal funds rate t… [+5200 chars]</t>
+        </is>
+      </c>
+      <c r="G584" t="n">
+        <v>0.1536</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/national-gas-prices-fall-again-203000950.html</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2025-12-08T20:30:00Z</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>National Gas Prices Fall Again To Multi-Year Lows</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>The national average price of gasoline has continued on a downward trend after dropping below $3 a gallon a week ago, sinking to their lowest level since...</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>The national average price of gasoline has continued on a downward trend after dropping below $3 a gallon a week ago, sinking to their lowest level since 2021. The median U.S. gas price is now $2.79 … [+2563 chars]</t>
+        </is>
+      </c>
+      <c r="G585" t="n">
+        <v>-0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gas-prices-fall-below-3-per-gallon-in-more-than-half-of-us-states-to-kick-off-thanksgiving-holiday-170628547.html</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Ines Ferré</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2025-11-25T17:06:28Z</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Gas prices fall below $3 per gallon in more than half of US states to kick off Thanksgiving holiday</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Gas prices are pennies away from $3 per gallon as the Thanksgiving driving season kicks off. A few lucky drivers in the Midwest are even seeing gas priced at...</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Gasoline prices are easing as the Thanksgiving travel weekend kicks off.
+While the national average remains slightly above $3 per gallon, the average price per gallon in more than half of US states … [+2287 chars]</t>
+        </is>
+      </c>
+      <c r="G586" t="n">
+        <v>0.5719</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gunvor-eyes-investment-u-oil-063000393.html</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2025-12-01T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Gunvor Eyes Investment in U.S. Oil and Gas</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Gunvor is exploring U.S. oil and gas asset purchases—primarily in natural gas—to strengthen ties with the Trump administration and expand its American...</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Swiss commodity trading major Gunvor is considering asset purchases in the U.S. oil and gas space, Reuters has reported, citing unnamed sources, in a bid to build a better relationship with the Trump… [+2197 chars]</t>
+        </is>
+      </c>
+      <c r="G587" t="n">
+        <v>0.6597</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-inch-higher-hitting-034227489.html</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2025-11-26T03:42:27Z</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Oil Prices Inch Higher After Hitting One-Month Lows</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Oil prices saw a small rebound in early Asian trading, but bearish sentiment persists as peace talks, weak demand, and OPEC+ supply growth overshadow...</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Oil prices recovered slightly in early Asian trading on Wednesday after falling to one-month lows in Tuesday's session. Sentiment in markets remains bearish, with traders focused on a potential peace… [+2208 chars]</t>
+        </is>
+      </c>
+      <c r="G588" t="n">
+        <v>-0.1531</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tullow-oil-names-roald-goethe-120000878.html</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2025-12-01T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Tullow Oil Names Roald Goethe Chair as It Executes Major Board Shake-Up</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Tullow Oil appoints Roald Goethe as independent chair amid sweeping board changes.</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Tullow Oil has appointed veteran oil trader and long-standing board member Roald Goethe as independent non-executive chair, effective 1 December 2025, in a move that coincides with a sweeping reducti… [+3140 chars]</t>
+        </is>
+      </c>
+      <c r="G589" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/kolibri-kgei-shareholders-approve-cap-164957242.html</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2025-12-09T16:49:57Z</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Kolibri (KGEI) Shareholders Approve Cap on Authorized Common Shares at 37.4M</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Kolibri Global Energy Inc. (NASDAQ:KGEI) is one of the cheap oil stocks under $10 to buy now. On November 25, Kolibri Global Energy Inc. (NASDAQ:KGEI...</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Kolibri Global Energy Inc. (NASDAQ:KGEI) is one of the cheap oil stocks under $10 to buy now. On November 25, Kolibri Global Energy Inc. (NASDAQ:KGEI) revealed that shareholders approved a resolution… [+1897 chars]</t>
+        </is>
+      </c>
+      <c r="G590" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jefferies-reaffirms-buy-vaalco-egy-164954022.html</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2025-12-09T16:49:54Z</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Jefferies Reaffirms Buy on VAALCO (EGY) Despite Q3 Revenue Miss</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>VAALCO Energy, Inc. (NYSE:EGY) is one of the cheap oil stocks under $10 to buy now. VAALCO Energy, Inc. (NYSE:EGY) holds a consensus Moderate Buy rating...</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>VAALCO Energy, Inc. (NYSE:EGY) is one of the cheap oil stocks under $10 to buy now. VAALCO Energy, Inc. (NYSE:EGY) holds a consensus Moderate Buy rating, with a single analyst setting a $7.27 target,… [+2228 chars]</t>
+        </is>
+      </c>
+      <c r="G591" t="n">
+        <v>0.5638</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/crescent-energy-crgy-posts-q3-164948181.html</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2025-12-09T16:49:48Z</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Crescent Energy (CRGY) Posts Q3 Miss but Keeps Buy Rating and $14 Target</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Crescent Energy Company (NYSE:CRGY) is one of the cheap oil stocks under $10 to buy now. On November 28, Siebert Williams Shank &amp; Co. stuck with a Buy rating...</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Crescent Energy Company (NYSE:CRGY) is one of the cheap oil stocks under $10 to buy now. On November 28, Siebert Williams Shank &amp;amp; Co. stuck with a Buy rating on Crescent Energy Company (NYSE:CRGY… [+1953 chars]</t>
+        </is>
+      </c>
+      <c r="G592" t="n">
+        <v>0.4678</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/roth-mkm-reaffirms-buy-highpeak-164956512.html</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2025-12-09T16:49:56Z</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Roth MKM Reaffirms Buy on HighPeak (HPK) Despite Weak Q3 Results</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>HighPeak Energy, Inc. (NASDAQ:HPK) is one of the cheap oil stocks under $10 to buy now. HighPeak Energy, Inc. (NASDAQ:HPK) carries a consensus Hold rating...</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>HighPeak Energy, Inc. (NASDAQ:HPK) is one of the cheap oil stocks under $10 to buy now. HighPeak Energy, Inc. (NASDAQ:HPK) carries a consensus Hold rating, based on one Buy and one Sell recommendatio… [+2453 chars]</t>
+        </is>
+      </c>
+      <c r="G593" t="n">
+        <v>0.6814</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bp-targets-450-000-bpd-171117980.html</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2025-12-08T17:11:17Z</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>BP Targets 450,000 bpd in New Iraq Field Redevelopment Push</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>British Petroleum is set to ramp up oil and gas production in northern Iraq, with plans to lift output at four key Kirkuk-area fields</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>British Petroleum is set to ramp up oil and gas production in northern Iraq, with plans to lift output at four key Kirkuk-area fields as part of a major redevelopment push backed by Baghdad. Accordin… [+2506 chars]</t>
+        </is>
+      </c>
+      <c r="G594" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/freedom-capital-downgrades-granite-ridge-164951274.html</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2025-12-09T16:49:51Z</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Freedom Capital Downgrades Granite Ridge (GRNT) to Hold, Cuts PT to $7</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Granite Ridge Resources, Inc. (NYSE:GRNT) is one of the cheap oil stocks under $10 to buy now. With two Hold ratings and no Buys or Sells, Granite Ridge...</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Granite Ridge Resources, Inc. (NYSE:GRNT) is one of the cheap oil stocks under $10 to buy now. With two Hold ratings and no Buys or Sells, Granite Ridge Resources, Inc. (NYSE:GRNT) carries a consensu… [+2269 chars]</t>
+        </is>
+      </c>
+      <c r="G595" t="n">
+        <v>0.2023</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-futures-slip-asian-stocks-050654089.html</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>ELAINE KURTENBACH</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2025-12-01T05:06:54Z</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>US futures slip and Asian stocks are mixed, while oil prices surge more than $1 a barrel</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Oil prices surged more than $1 a barrel.  In Japan, the Nikkei 225 declined 1.9% to 49,303.28 after the government reported weaker than expected corporate...</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>BANGKOK (AP) U.S. futures fell and Asian shares began the week mixed, with Tokyos benchmark falling nearly 2% on Monday after the release of data showing weak factory activity.
+Oil prices surged mor… [+4202 chars]</t>
+        </is>
+      </c>
+      <c r="G596" t="n">
+        <v>-0.3182</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ceasefire-speculation-tests-oil-floor-160000514.html</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2025-11-25T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Ceasefire Speculation Tests Oil’s Floor</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Media reports that the Trump administration is inching ever closer to a comprehensive peace deal between Russia and Ukraine has exerted additional pressure...</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Oil fell 2.5% on Tuesday morning following reports that Ukraine has mostly agreed to a peace deal with the U.S.
+European Gas Prices Chill at Lowest Levels Since May 2024
+- European gas prices have … [+6550 chars]</t>
+        </is>
+      </c>
+      <c r="G597" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ecopetrol-ec-falls-following-q3-024206716.html</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2025-11-28T02:42:06Z</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Ecopetrol (EC) Falls Following Q3 Results</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>The share price of Ecopetrol S.A. (NYSE:EC) fell by 5.46% between November 19 and November 26, 2025, putting it among the Energy Stocks that Lost the Most...</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>The share price of Ecopetrol S.A. (NYSE:EC) fell by 5.46% between November 19 and November 26, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Ecopetrol (EC) Falls Following Q… [+1596 chars]</t>
+        </is>
+      </c>
+      <c r="G598" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/suriname-long-awaited-oil-boom-210000178.html</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Matthew Smith</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2025-11-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Suriname’s Long-Awaited Oil Boom Finally Takes Shape</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Suriname’s long-stalled offshore oil ambitions are finally advancing, led by TotalEnergies and Petronas, creating hopes of an economic turnaround after years...</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>After the discovery of oil in Surinames territorial waters in January 2020, the government in the capital Paramaribo pitched its hopes on an oil boom matching that of neighboring Guyana. You see, dec… [+6697 chars]</t>
+        </is>
+      </c>
+      <c r="G599" t="n">
+        <v>0.4215</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/60-oil-no-longer-floor-160000123.html</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2025-12-19T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>$60 Oil Is No Longer a Floor</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Brent is clinging to $60 per barrel, but markets have become even less sensitive to geopolitical risk.</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Brent is clinging to $60 per barrel, but markets have become even less sensitive to geopolitical risk.
+Friday, December 19, 2025 
+Things are not looking good for oil, with Trumps belligerent rhetor… [+5013 chars]</t>
+        </is>
+      </c>
+      <c r="G600" t="n">
+        <v>-0.7476</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/iran-hikes-gasoline-prices-first-010000014.html</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2025-12-16T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Iran Hikes Gasoline Prices For The First Time Since 2019</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>The Islamic Republic of Iran has announced a fuel price hike for the first time since 2019, with the increase coming at a time when the authorities are...</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>The Islamic Republic of Iran has announced a fuel price hike for the first time since 2019, with the increase coming at a time when the authorities are struggling with economic pressures and environm… [+5225 chars]</t>
+        </is>
+      </c>
+      <c r="G601" t="n">
+        <v>-0.4215</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/opec-expected-extend-pause-oil-153500124.html</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2025-11-27T15:35:00Z</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>OPEC+ Expected to Extend Pause on Oil Hikes as Prices Stay Weak</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>OPEC+ members are expected to stick with their decision to pause oil production increases when the group meets online this Sunday, signaling a cautious...</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>OPEC+ members are expected to stick with their decision to pause oil production increases when the group meets online this Sunday, signaling a cautious approach amid growing signs of oversupply and p… [+2902 chars]</t>
+        </is>
+      </c>
+      <c r="G602" t="n">
+        <v>-0.2263</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-gains-while-nasdaq-sp-500-slide-as-oracle-earnings-revive-ai-spending-fears-233526438.html</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2025-12-10T23:35:26Z</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow gains while Nasdaq, S&amp;P 500 slide as Oracle earnings revive AI spending fears</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Oracle's revenue miss is reviving the AI bubble debate, dampening spirits on Wall Street.</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>US stocks traded mixed at the market open on Thursday, with a tumble for Oracle (ORCL) putting more tech-exposed gauges under pressure after its earnings revived AI overspending worries.
+The Nasdaq … [+9051 chars]</t>
+        </is>
+      </c>
+      <c r="G603" t="n">
+        <v>-0.4588</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-futures-rise-as-oil-climbs-and-wall-street-weighs-jobs-data-signals-235109965.html</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Karen Friar</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2025-12-16T23:51:09Z</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures rise as oil climbs and Wall Street weighs jobs data signals</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Stocks are leaning higher as oil gains after Trump placed a blockade on tankers off Venezuela.</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>US stock futures rose on Wednesday, poised to backtrack on a string of recent slumps as oil surged and investors continued to debate what the latest jobs data means for Federal Reserve policy and the… [+5686 chars]</t>
+        </is>
+      </c>
+      <c r="G604" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/benchmark-diesel-price-declines-four-162941902.html</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>John Kingston</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2025-11-25T16:29:41Z</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Benchmark diesel price declines after four weeks of increases</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>The benchmark diesel price used for most fuel surcharges declined after four weeks of increases. The post Benchmark diesel price declines after four weeks of...</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>After several wild weeks of movement in diesel prices, at times rising far faster than any movement in crude prices would justify, the benchmark price used for most fuel surcharges fell after four we… [+4470 chars]</t>
+        </is>
+      </c>
+      <c r="G605" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/benchmark-diesel-posts-biggest-1-165435186.html</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>John Kingston</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2025-12-02T16:54:35Z</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Benchmark diesel posts its biggest 1-week decline in almost a year</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>The benchmark diesel price used for most fuel surcharges is down 11 cents/gallon in two weeks. The post Benchmark diesel posts its biggest 1-week decline in ...</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Its been almost a year since the benchmark diesel price used for most fuel surcharges fell as much as it did in its most recent posting Tuesday.
+The Department of Energy/Energy Information Administr… [+4356 chars]</t>
+        </is>
+      </c>
+      <c r="G606" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ubs-believes-diamondback-energy-fang-195245494.html</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2025-12-19T19:52:45Z</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>UBS Believes Diamondback Energy (FANG) is Poised for a 2026 Breakout Following Period of Stagnation</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Diamondback Energy Inc. (NASDAQ:FANG) is one of the most profitable value stocks to invest in right now. On December 12, UBS raised the firm’s price target...</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Diamondback Energy Inc. (NASDAQ:FANG) is one of the most profitable value stocks to invest in right now. On December 12, UBS raised the firms price target on Diamondback Energy to $194 from $174 and … [+2376 chars]</t>
+        </is>
+      </c>
+      <c r="G607" t="n">
+        <v>0.9036</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/piper-sandler-lowers-eog-price-055952266.html</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Vardah Gill</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2025-11-26T05:59:52Z</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Piper Sandler Lowers EOG Price Target to $124, Maintains Neutral Rating</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>EOG Resources, Inc. (NYSE:EOG) is included among the 15 Best Stocks to Buy for Medium Term. On November 18, Pip‌er San‌d‌ler cut its pri⁠ce target on EOG...</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>EOG Resources, Inc. (NYSE:EOG) is included among the 15 Best Stocks to Buy for Medium Term.
+Piper Sandler Lowers EOG Price Target to $124, Maintains Neutral Rating
+On November 18, Piper Sandler cut… [+1712 chars]</t>
+        </is>
+      </c>
+      <c r="G608" t="n">
+        <v>0.4939</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ai-becomes-boost-global-oil-220000970.html</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2025-12-10T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>AI Becomes a Boost for Global Oil Demand, Not a Bridge to Net Zero</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>While climate advocates warn AI may stall the energy transition, the technology is already helping producers cut costs and boost recovery.</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Artificial intelligence could help the energy industry tap an additional one trillion barrels of oil by making more of these barrels economical to extract. Wood Mackenzie analysts made the prediction… [+5421 chars]</t>
+        </is>
+      </c>
+      <c r="G609" t="n">
+        <v>0.8442</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/wall-street-cautious-conocophillips-cop-123255387.html</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Talha Qureshi</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2025-12-11T12:32:55Z</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Wall Street Cautious on ConocoPhillips (COP), Here’s Why</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>​ConocoPhillips (NYSE:COP) is one of the Cheap NYSE Stocks to Buy Now. Wall Street has a cautious outlook on ConocoPhillips (NYSE:COP), mainly due to the...</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is one of the Cheap NYSE Stocks to Buy Now. Wall Street has a cautious outlook on ConocoPhillips (NYSE:COP), mainly due to the supply-side risks facing the oil and liquids s… [+2382 chars]</t>
+        </is>
+      </c>
+      <c r="G610" t="n">
+        <v>-0.4404</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crude_oil_sentiment_score_.xlsx
+++ b/data/crude_oil_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G610"/>
+  <dimension ref="A1:G710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22078,6 +22078,3435 @@
         <v>-0.4404</v>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>https://uk.finance.yahoo.com/news/bp-cautions-over-weak-oil-082253363.html</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Holly Williams, Press Association Business Editor</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2026-01-15T11:46:16Z</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>BP cautions over ‘weak’ oil trading and reveals up to £3.7bn in write-downs</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>The oil giant joined FTSE 100 rival Shell, after it also last week cautioned over a weaker performance from oil trading amid lower crude costs.</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>BP has warned it expects to book up to five billion dollars (£3.7 billion) in write-downs across its gas and low-carbon energy division as it also said oil trading had been weak in its final quarter.… [+1752 chars]</t>
+        </is>
+      </c>
+      <c r="G611" t="n">
+        <v>-0.4404</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exclusive-valero-buys-venezuelan-oil-011130571.html</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney and Arathy Somasekhar</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2026-01-22T01:11:30Z</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Exclusive-Valero buys Venezuelan oil cargo as part of Washington's deal with Caracas</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney and Arathy Somasekhar HOUSTON, Jan 21 (Reuters) - Valero bought a cargo of Venezuelan crude oil, two sources said on Wednesday, the...</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>By Georgina McCartney and Arathy Somasekhar
+HOUSTON, Jan 21 (Reuters) - Valero bought a cargo of Venezuelan crude oil, two sources said on Wednesday, the first deal by a U.S. Gulf Coast refiner stru… [+987 chars]</t>
+        </is>
+      </c>
+      <c r="G612" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/vitol-trafigura-offer-venezuelan-oil-111008014.html</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma and Siyi Liu</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2026-01-12T11:10:08Z</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Vitol, Trafigura offer Venezuelan oil to Indian, Chinese refiners for March delivery, sources say</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma and Siyi Liu NEW DELHI/SINGAPORE, Jan 12 (Reuters) - Vitol and Trafigura have started discussions on Venezuelan crude oil sales with refiners ...</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma and Siyi Liu
+NEW DELHI/SINGAPORE, Jan 12 (Reuters) - Vitol and Trafigura have started discussions on Venezuelan crude oil sales with refiners in India and China for cargoes to be deli… [+2364 chars]</t>
+        </is>
+      </c>
+      <c r="G613" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/indias-reliance-buy-sanctions-compliant-132556976.html</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2026-01-21T13:25:56Z</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>India's Reliance to buy sanctions-compliant Russian oil in February and March, sources say</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma NEW DELHI/MOSCOW, Jan 21 (Reuters) - India's Reliance Industries Ltd, operator of the world's largest refining complex, is set to receive...</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>By Nidhi Verma
+NEW DELHI/MOSCOW, Jan 21 (Reuters) - India's Reliance Industries Ltd, operator of the world's largest refining complex, is set to receive sanctions-compliant Russian oil in February a… [+2031 chars]</t>
+        </is>
+      </c>
+      <c r="G614" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>https://ca.finance.yahoo.com/news/trading-houses-beat-us-majors-115729637.html</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>By Dmitry Zhdannikov, Marianna Parraga and Shariq Khan</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2026-01-12T11:57:29Z</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Trading houses beat US majors to first deals for Venezuelan oil</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>By Dmitry Zhdannikov, Marianna Parraga and Shariq Khan LONDON, Jan 12 (Reuters) - Global oil trading houses have emerged as early winners in the race to...</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>By Dmitry Zhdannikov, Marianna Parraga and Shariq Khan
+LONDON, Jan 12 (Reuters) - Global oil trading houses have emerged as early winners in the race to control Venezuelan crude flows, getting ahead… [+7066 chars]</t>
+        </is>
+      </c>
+      <c r="G615" t="n">
+        <v>-0.1531</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/why-boosting-production-venezuelas-very-150149908.html</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>STEVEN GRATTAN</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2026-01-09T15:01:49Z</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Why boosting production of Venezuela's 'very dense, very sloppy' oil could harm the environment</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Environmental experts are warning that the U.S. push to revamp and boost Venezuela’s vast oil reserves could worsen decades of ecological damage and increase...</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>BOGOTA, Colombia (AP) Environmental experts are warning that the U.S. push to revamp and boost Venezuelas vast oil reserves could worsen decades of ecological damage and increase planet-warming pollu… [+8545 chars]</t>
+        </is>
+      </c>
+      <c r="G616" t="n">
+        <v>-0.7184</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/factbox-white-house-gathers-oil-110226050.html</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>By Jarrett Renshaw</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2026-01-09T11:13:13Z</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Factbox-White House gathers oil majors, traders, drillers on Venezuela</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>By Jarrett Renshaw Jan 9 (Reuters) - The White House is convening a meeting on Friday with major U.S. and international oil companies to discuss potential...</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>By Jarrett Renshaw
+Jan 9 (Reuters) - The White House is convening a meeting on Friday with major U.S. and international oil companies to discuss potential investment in Venezuelas energy sector, as … [+816 chars]</t>
+        </is>
+      </c>
+      <c r="G617" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exclusive-kazakhstans-tengiz-oilfield-seen-135758163.html</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2026-01-27T13:57:58Z</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Exclusive-Kazakhstan's Tengiz oilfield seen recovering less than half its output by February 7, sources say</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>MOSCOW, Jan 27 () - Kazakhstan's biggest oilfield, Tengiz, is likely to have restored less than half of its normal production by February 7 as it slowly...</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>MOSCOW, Jan 27 (Reuters) - Kazakhstan's biggest oilfield, Tengiz, is likely to have restored less than half of its normal production by February 7 as it slowly recovers from a fire and power outage, … [+2352 chars]</t>
+        </is>
+      </c>
+      <c r="G618" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_33c4cbde-25ec-4955-938b-43750275e5ef</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr"/>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2026-01-05T19:26:28Z</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Why Big Oil has a long road ahead in Venezuela, the 'fallen angel of global crude markets'</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr"/>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G619" t="n">
+        <v>-0.4019</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>https://ca.news.yahoo.com/exclusive-mexico-weighs-stopping-oil-193113164.html</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>By Diego Oré</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2026-01-23T19:31:13Z</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Exclusive-Mexico weighs stopping oil shipments to Cuba amid concerns of Trump retaliation, sources say</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>By Diego Oré MEXICO CITY, Jan 23 (Reuters) - The Mexican government is reviewing whether to keep sending oil to Cuba amid growing fears within President...</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>By Diego Oré
+MEXICO CITY, Jan 23 (Reuters) - The Mexican government is reviewing whether to keep sending oil to Cuba amid growing fears within President Claudia Sheinbaum's administration that Mexic… [+6486 chars]</t>
+        </is>
+      </c>
+      <c r="G620" t="n">
+        <v>-0.4019</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/trump-warns-higher-tariffs-india-043546611.html</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2026-01-05T04:35:46Z</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Trump warns of higher tariffs on India over Russian oil purchases</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>NEW DELHI, Jan 5 () - The United States could raise tariffs on India if New Delhi doesn't meet Washington's demand ​to curb purchases of Russian oil...</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>NEW DELHI, Jan 5 (Reuters) - The United States could raise tariffs on India if New Delhi doesn't meet Washington's demand to curb purchases of Russian oil, President Donald Trump told reporters aboar… [+1500 chars]</t>
+        </is>
+      </c>
+      <c r="G621" t="n">
+        <v>0.4157</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-inclined-keep-exxonmobil-venezuela-004509652.html</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>SEUNG MIN KIM AND JULIA NIKHINSON</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2026-01-12T00:45:09Z</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Trump 'inclined' to keep ExxonMobil out of Venezuela after CEO response at White House meeting</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>President Donald Trump said Sunday that he is “inclined” to keep ExxonMobil out of Venezuela after its top executive was skeptical about oil investment...</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>ABOARD AIR FORCE ONE (AP) President Donald Trump said Sunday that he is inclined to keep ExxonMobil out of Venezuela after its top executive was skeptical about oil investment efforts in the country … [+1580 chars]</t>
+        </is>
+      </c>
+      <c r="G622" t="n">
+        <v>0.0857</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/clock-ticks-cuba-trump-cuts-110821648.html</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>By Dave Sherwood  and Marianna Parraga</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2026-01-13T11:08:21Z</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Clock ticks in Cuba as Trump cuts off Venezuelan oil</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>By Dave Sherwood and Marianna Parraga HAVANA/HOUSTON, Jan 13 (Reuters) - Cubans are bracing for impact after U.S.</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>By Dave Sherwood and Marianna Parraga
+HAVANA/HOUSTON, Jan 13 (Reuters) - Cubans are bracing for impact after U.S. President Donald Trump vowed to cut off a lifeline of Venezuelan oil from reaching C… [+4467 chars]</t>
+        </is>
+      </c>
+      <c r="G623" t="n">
+        <v>-0.3612</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/panama-says-canceled-flag-us-221704732.html</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2026-01-08T22:17:04Z</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Panama says it canceled flag of US-seized oil tanker a year ago</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>PANAMA CITY, Jan 8 (Reuters) - Panama's maritime authority on Thursday said it had canceled in January of last year the flag of the M Sophia, a Venezuela...</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>PANAMA CITY, Jan 8 (Reuters) - Panama's maritime authority on Thursday said it had canceled in January of last year the flag of the M Sophia, a Venezuela-linked oil tanker seized by the U.S. military… [+1664 chars]</t>
+        </is>
+      </c>
+      <c r="G624" t="n">
+        <v>0.0772</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-the-stock-market-is-shrugging-off-venezuelan-leader-nicolas-maduros-capture-205110221.html</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Brooke DiPalma</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2026-01-05T20:51:10Z</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Why the stock market is 'shrugging off' Venezuelan leader Nicolás Maduro's capture</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Markets seem to be shrugging off the latest geopolitical tension at first blush.</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Early Monday morning, Ed Yardeni, president of Yardeni Research, wrote in a note to clients that he was adding Venezuela "to our list of unsettling developments" that could factor into a volatile sta… [+3777 chars]</t>
+        </is>
+      </c>
+      <c r="G625" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/trump-china-problem-venezuela-beijings-010046974.html</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>DIDI TANG and BERNARD CONDON</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2026-01-09T01:00:46Z</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Trump has a China problem in Venezuela: What to do with Beijing's debt and oil stakes</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>When it comes to claiming that Venezuelan oil is now under his control, President Donald Trump is mincing no words.  After all, Trump is expected to visit...</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>WASHINGTON (AP) When it comes to claiming that Venezuelan oil is now under his control, President Donald Trump is mincing no words. But no small part of that oil belongs to China under contracts it s… [+6143 chars]</t>
+        </is>
+      </c>
+      <c r="G626" t="n">
+        <v>-0.7184</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>https://uk.finance.yahoo.com/news/gold-prices-greenland-trump-oil-pound-latest-112134371.html</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Vicky McKeever</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2026-01-21T11:21:34Z</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Gold prices surge past $4,800 on jitters over Greenland dispute</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Gold prices extended recent gains on Wednesday, surging on concerns about escalating tensions over US president Donald Trump's push to take over Greenland.</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Gold prices extended recent gains on Wednesday morning, surging on concerns about escalating tensions over US president Donald Trump's push to take over Greenland.
+Gold futures (GC=F) jumped 2% to $… [+3212 chars]</t>
+        </is>
+      </c>
+      <c r="G627" t="n">
+        <v>-0.4588</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/top-three-dividend-stocks-consider-173204675.html</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Simply Wall St</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2026-01-26T17:32:04Z</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Top Three Dividend Stocks To Consider In Your Portfolio</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>As the U.S. stock market kicks off a pivotal week with major tech earnings and geopolitical tensions influencing investor sentiment, dividend stocks continue...</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>As the U.S. stock market kicks off a pivotal week with major tech earnings and geopolitical tensions influencing investor sentiment, dividend stocks continue to draw attention as a potential source o… [+4917 chars]</t>
+        </is>
+      </c>
+      <c r="G628" t="n">
+        <v>-0.2263</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-russias-diesel-exports-suddenly-230000342.html</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Natalia Katona</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2026-01-22T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Why Russia's Diesel Exports Are Suddenly Soaring</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Russian diesel exports rebounded to around 900,000 b/d in December (after falling to a five-year low of 590,000 b/d in September), as refinery runs recovered...</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Russian diesel has moved from being the main bullish factor in global middle-distillate markets in 2025 to an overwhelmingly bearish force by early 2026, reversing a year-long surge in refining margi… [+7079 chars]</t>
+        </is>
+      </c>
+      <c r="G629" t="n">
+        <v>-0.128</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-futures-edge-higher-gold-045146410.html</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>CHAN HO-HIM</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2026-01-21T04:51:46Z</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>US futures edge higher and gold hits another record as markets swoon over Greenland dispute</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Asian shares mostly extended their losses on Wednesday and gold prices hit a record high as concerns over U.S. President Donald Trump’s tariff threats on...</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>HONG KONG (AP) Asian shares mostly extended their losses on Wednesday and gold prices hit a record high as concerns over U.S. President Donald Trumps tariff threats on Greenland fueled unease among i… [+3464 chars]</t>
+        </is>
+      </c>
+      <c r="G630" t="n">
+        <v>-0.8270999999999999</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/irans-traders-frustrated-economic-losses-160902483.html</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>By Parisa Hafezi</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2026-01-12T16:13:11Z</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Iran's traders, frustrated by economic losses, turn against clerics</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>By Parisa Hafezi DUBAI, Jan 12 (Reuters) - Iran's bazaar merchants, the trader class who were the financial backbone of the 1979 Islamic Revolution, have...</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>By Parisa Hafezi
+DUBAI, Jan 12 (Reuters) - Iran's bazaar merchants, the trader class who were the financial backbone of the 1979 Islamic Revolution, have turned against the clerics they helped bring… [+5252 chars]</t>
+        </is>
+      </c>
+      <c r="G631" t="n">
+        <v>-0.7269</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-futures-sink-trump-warns-064219353.html</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>ELAINE KURTENBACH</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2026-01-19T06:42:19Z</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>US futures sink after Trump warns of higher tariffs for 8 countries over Greenland issue</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>U.S. stock futures skidded Monday after U.S. President Donald Trump threatened to slap a 10% extra tariff on imports from eight European countries due to...</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>BANGKOK (AP) U.S. stock futures skidded Monday after U.S. President Donald Trump threatened to slap a 10% extra tariff on imports from eight European countries due to their opposition to his desire t… [+3982 chars]</t>
+        </is>
+      </c>
+      <c r="G632" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/enterprise-products-epd-downgraded-raymond-220602989.html</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Vardah Gill</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2026-01-12T22:06:02Z</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Enterprise Products (EPD) Downgraded at Raymond James as Midstream Focus Shifts to Execution</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Enterprise Products Partners L.P. (NYSE:EPD) is included among the 13 Best Dividend Stocks Paying Over 6%. On January 5, Raymond James downgraded Enterprise ...</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Enterprise Products Partners L.P. (NYSE:EPD) is included among the 13 Best Dividend Stocks Paying Over 6%.
+Enterprise Products (EPD) Downgraded at Raymond James as Midstream Focus Shifts to Executio… [+2322 chars]</t>
+        </is>
+      </c>
+      <c r="G633" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>https://uk.news.yahoo.com/trump-sets-sights-greenland-193706716.html</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Cameron Henderson</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2026-01-04T19:37:06Z</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Trump sets sights on Greenland</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Donald Trump has signalled that Greenland is in his sights after capturing Nicolas Maduro, the Venezuelan dictator, and taking him to the US to face trial.</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Donald Trump has signalled that Greenland is in his sights after capturing Nicolas Maduro, the Venezuelan dictator, and taking him to the US to face trial.
+We do need Greenland, absolutely, the US p… [+8313 chars]</t>
+        </is>
+      </c>
+      <c r="G634" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/plains-gp-holdings-pagp-pricing-211139932.html</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Simply Wall St</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2026-01-09T21:11:39Z</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Is Plains GP Holdings (PAGP) Pricing Reflect Long Term Energy Infrastructure Demand?</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>If you are wondering whether Plains GP Holdings shares still offer value at around US$19.61, you are not alone. This article is built to help you frame that ...</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;&lt;li&gt;If you are wondering whether Plains GP Holdings shares still offer value at around US$19.61, you are not alone. This article is built to help you frame that question clearly.
+&lt;/li&gt;&lt;li&gt;The st… [+5824 chars]</t>
+        </is>
+      </c>
+      <c r="G635" t="n">
+        <v>0.8844</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_410a62d7-97ac-4b35-98d4-3c4b93a133c3</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr"/>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2026-01-26T17:00:30Z</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Crude Oil Falls Back as Kazakhstan's Oil Disruptions Ease</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G636" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-says-deeply-shocked-us-145527537.html</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Bloomberg News</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2026-01-03T16:37:36Z</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Beijing Slams America's 'Hegemonic Acts'...</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Beijing Slams America's 'Hegemonic Acts'...
+ (Top headline, 5th story, link)
+ Related stories:TRUMP NEWS CONFERENCE... DEVELOPING...
+Venezuela Accuses USA Of Attacking Residential Areas...
+Claims innocent civilians killed...
+Chinese del…</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- China said its deeply shocked by the USs military strikes on Venezuela and its capture of President Nicolas Maduro.
+China strongly condemns the USs blatant use of force against a sove… [+3609 chars]</t>
+        </is>
+      </c>
+      <c r="G637" t="n">
+        <v>-0.7425</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_ae4b4ea7-d2aa-4dd5-a19e-f4a8c9472aa0</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr"/>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2026-01-06T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Oil ETFs Rise as Investors Hedge Crude Futures Exposure</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G638" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_e8c8fda9-0b77-40a3-931c-c675ee95fffc</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2026-01-23T20:17:22Z</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Crude Oil Rallies on Dollar Weakness and Heightened Geopolitical Risks</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G639" t="n">
+        <v>-0.6249</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_4d1f5096-d802-499b-93bf-d9798fbdcf67</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr"/>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2026-01-27T17:34:14Z</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Return of Venezuelan crude could cut US fuel oil imports</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G640" t="n">
+        <v>-0.3182</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_9e053f74-5aff-4432-9134-62a2e02e89aa</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr"/>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2026-01-20T16:38:02Z</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Dollar Strength and Smaller Global Supplies Lift Crude Oil Prices</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G641" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venezuelan-oil-limits-u-refining-010000340.html</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2026-01-14T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Venezuelan Oil and the Limits of U.S. Refining Capacity</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Venezuelan crude is attractive to complex U.S. refiners with coking capacity, but only a subset of Gulf and East Coast plants can fully process the heavy...</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Last week, U.S. President Donald Trumps Venezuela pitch to oil executives to invest the vast sums required to revive the countrys flagging oil sector proved largely ineffectual. Exxon Mobil (NYSE:XOM… [+6114 chars]</t>
+        </is>
+      </c>
+      <c r="G642" t="n">
+        <v>0.0516</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-venezuela-oil-plan-runs-180000464.html</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Andrew Topf</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2026-01-13T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Trump’s Venezuela Oil Plan Runs Into Hard Reality</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Venezuela’s oil is mostly extra-heavy crude from the Orinoco Belt, with breakeven costs above $80 per barrel—making it uneconomic at current prices and far...</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Last week US President Donald Trump announced that Venezuela’s interim authorities will turn over up to 50 million barrels of oil to the United States, before later declaring his administration will … [+6917 chars]</t>
+        </is>
+      </c>
+      <c r="G643" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-slips-eia-reports-crude-165323893.html</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Julianne Geiger</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2026-01-07T16:53:23Z</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Oil Slips as EIA Reports Crude Draw, Sharp Builds in Gasoline, Distillate Stocks</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Crude oil inventories in the United States posted a sharp draw last week, even as gasoline and distillate stockpiles recorded sizable builds, according to...</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Crude oil inventories in the United States posted a sharp draw last week, even as gasoline and distillate stockpiles recorded sizable builds, according to new data released Wednesday by the U.S. Ener… [+2371 chars]</t>
+        </is>
+      </c>
+      <c r="G644" t="n">
+        <v>-0.6808</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/stocks-bonds-set-jittery-start-204423169.html</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Anand Krishnamoorthy</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2026-01-04T20:44:23Z</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Stocks, Bonds Set for Jittery Start on Venezuela: Markets Wrap</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Although Venezuela isn’t a top-20 crude producer, any persistent increase in oil prices and its inflationary impact on economies pose a risk for markets...</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>(Bloomberg) Global financial markets face a skittish open after the US ousted Venezuelas president, triggering a fresh geopolitical flashpoint that intensifies regional risk and raises some questions… [+4798 chars]</t>
+        </is>
+      </c>
+      <c r="G645" t="n">
+        <v>0.0516</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/market-minute-1-5-26-140900271.html</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>MoneyShow</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2026-01-05T14:09:00Z</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Market Minute 1-5-26- Energy Stocks, Gold Jump After Maduro Raid</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Stocks are mixed in the early going today, while gold and silver are jumping again. Crude oil is modestly higher along with the dollar, while Treasuries are ...</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Stocks are mixed in the early going today, while gold and silver are jumping again. Crude oil is modestly higher along with the dollar, while Treasuries are flat.
+To get more articles and chart anal… [+1955 chars]</t>
+        </is>
+      </c>
+      <c r="G646" t="n">
+        <v>-0.1779</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/analysis-venezuelan-oil-boost-us-185000056.html</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar and Georgina McCartney</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2026-01-06T18:50:00Z</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Analysis-Venezuelan oil would boost US refiners, hurt Canadian producers</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>HOUSTON, Jan 6 (Reuters) - A full-scale resumption of Venezuelan oil exports would benefit refiners in the United States and lower their fuel production...</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar and Georgina McCartney
+HOUSTON, Jan 6 (Reuters) - A full-scale resumption of Venezuelan oil exports would benefit refiners in the United States and lower their fuel production c… [+5060 chars]</t>
+        </is>
+      </c>
+      <c r="G647" t="n">
+        <v>0.4404</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/why-southeast-asia-online-scam-083456035.html</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Associated Press</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2026-01-08T08:34:56Z</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Why Southeast Asia’s online scam industry is so hard to shut down</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Cambodia’s arrest and extradition of a powerful tycoon accused of running a vast online scam network marks a rare strike against an industry that has stolen ...</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>KUALA LUMPUR, Malaysia (AP) Cambodias arrest and extradition of a powerful tycoon accused of running a vast online scam network marks a rare strike against an industry that has stolen tens of billion… [+6452 chars]</t>
+        </is>
+      </c>
+      <c r="G648" t="n">
+        <v>-0.9296</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/know-protests-now-shaking-iran-054316165.html</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>JON GAMBRELL</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2026-01-04T05:43:16Z</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>What to know about the protests now shaking Iran as tensions remain high over its nuclear program</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Widening protests in Iran sparked by the Islamic Republic's ailing economy are putting new pressure on its theocracy.  Tehran is still reeling from a 12-day ...</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>DUBAI, United Arab Emirates (AP) Widening protests in Iran sparked by the Islamic Republic's ailing economy are putting new pressure on its theocracy.
+Tehran is still reeling from a 12-day war launc… [+6131 chars]</t>
+        </is>
+      </c>
+      <c r="G649" t="n">
+        <v>-0.8591</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chevron-set-increase-venezuelan-crude-175310421.html</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2026-01-30T17:53:10Z</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Chevron Set to Increase Venezuelan Crude Oil Exports to the United States</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 10 Best American Oil and Gas Stocks to Buy. Chevron Corporation (NYSE:CVX) manufactures and sells a...</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 10 Best American Oil and Gas Stocks to Buy.
+Chevron Set to Increase Venezuelan Crude Oil Exports to the United States
+Chevron Corporation (NYSE:… [+1634 chars]</t>
+        </is>
+      </c>
+      <c r="G650" t="n">
+        <v>0.7184</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chinese-refiners-expected-replace-venezuelan-115343414.html</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>By Siyi Liu and Florence Tan</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2026-01-07T11:53:43Z</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Chinese refiners expected to replace Venezuelan oil with Iranian crude, traders say</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>SINGAPORE, Jan 7 (Reuters) - Chinese independent refiners are expected to switch to heavy crude from sources including Iran in coming months to replace...</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>By Siyi Liu and Florence Tan
+SINGAPORE, Jan 7 (Reuters) - Chinese independent refiners are expected to switch to heavy crude from sources including Iran in coming months to replace Venezuelan shipme… [+2340 chars]</t>
+        </is>
+      </c>
+      <c r="G651" t="n">
+        <v>-0.8126</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/markets-price-chaos-oil-finds-154342248.html</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2026-01-13T15:43:42Z</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Markets Price Chaos as Oil Finds Its Footing</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Oil prices have rebounded sharply on geopolitical risk despite no meaningful supply losses.</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Oil prices have rebounded sharply on geopolitical risk despite no meaningful supply losses.
+Call Options Go Wild as Brent Traders Bet Big on Chaos
+- Iran protests and the increasing probability tha… [+6742 chars]</t>
+        </is>
+      </c>
+      <c r="G652" t="n">
+        <v>-0.9213</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-venezuela-gambit-could-erode-220000681.html</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2026-01-12T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Trump’s Venezuela Gambit Could Erode OPEC’s Clout in Oil Markets</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Rising oil output from the Americas and potential U.S. control over Venezuela’s reserves threaten to weaken OPEC’s influence on global oil supply and pricing...</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>For the past year, surging oil production from the Americas – led by the United States, Guyana, and Brazil – has been a headache for OPEC in its efforts to rebalance the market and seek higher oil pr… [+4463 chars]</t>
+        </is>
+      </c>
+      <c r="G653" t="n">
+        <v>0.4215</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-problem-isn-t-iran-000000686.html</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2026-01-18T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Oil’s Problem Isn’t Iran or Russia — It’s Too Much Oil</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Oil prices are retreating after a geopolitics-driven spike, as the glut narrative regains control.</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Crude oil prices are in retreat after rising on the possibility of U.S. strikes on Iran. Before the retreat, however, Brent crude and WTI had jumped to the highest in months, countering bearish forec… [+5358 chars]</t>
+        </is>
+      </c>
+      <c r="G654" t="n">
+        <v>-0.875</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/kurdistan-oil-lifeline-risk-baghdad-210000349.html</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Simon Watkins</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2026-01-20T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Kurdistan’s Oil Lifeline at Risk as Baghdad Payments Fall Short Again</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Despite resuming limited exports via the ITP and transferring oil and non-oil revenues to Baghdad, the KRG says promised payments and investment funding have...</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>The Kurdistan Region of Iraq (KRI) is once again edging toward a fiscal breaking point. Officials in its Erbil-based semi-autonomous regional government (KRG) say they are receiving only a fraction o… [+7462 chars]</t>
+        </is>
+      </c>
+      <c r="G655" t="n">
+        <v>-0.2732</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_b373c024-c2ca-415f-81e0-3f0967c3dcce</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr"/>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2026-01-08T20:19:50Z</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Crude Sharply Higher on Energy Demand Strength and Index Buying of Oil Futures</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G656" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_df7a3a67-3cac-4ec4-a737-9469fb14b13e</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr"/>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>2026-01-19T04:20:45Z</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Diamondback (FANG) Says Realized Oil Prices Fell in Q4 as Crude Market Weakened</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G657" t="n">
+        <v>-0.3612</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_efa5778f-b990-422c-8959-d668506ae58b</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr"/>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>2026-01-20T20:19:21Z</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Crude Rallies as the Dollar Falls and Black Sea Oil Production Disrupted</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G658" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venezuela-becomes-major-oil-producer-152915336.html</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Josh Funk, The Associated Press</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2026-01-04T15:29:15Z</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>If Venezuela becomes a major oil producer again, ‘that could cement lower prices’ long term and put pressure on Russia, analyst says</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>“There’s been a big benefit for Russia to see Venezuela’s oil industry collapse. And the reason is because they were a competitor on the global stage for...</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>President Donald Trump’s plan to take control of Venezuela’s oil industry and ask American companies to revitalize it after capturing President Nicolás Maduro in a raid isn’t likely to have a signifi… [+6022 chars]</t>
+        </is>
+      </c>
+      <c r="G659" t="n">
+        <v>-0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-slide-after-trump-picks-warsh-for-fed-gold-silver-plunge-181435040.html</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2026-01-30T18:14:35Z</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq slide after Trump picks Warsh for Fed; gold, silver plunge</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Major gauges are set to end the week higher with earnings and the Fed holding investor attention.</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>US stocks slid on Friday as President Trump said he would nominate Kevin Warsh to lead the Federal Reserve, against a background of a rising dollar and a screeching halt to 2026's roaring metals rall… [+16045 chars]</t>
+        </is>
+      </c>
+      <c r="G660" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jim-mellon-says-venezuelas-oil-230212952.html</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Vishaal Sanjay</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>2026-01-10T23:02:12Z</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Jim Mellon Says Venezuela's Oil Recovery Is 5+ Years Away, But US Refiners Could Benefit: 'I'd Suggest Loading Up On Oil And Gas'</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Billionaire investor Jim Mellon said that Venezuela’s oil industry faces a long and difficult road to recovery, with meaningful production gains unlikely to ...</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Billionaire investor Jim Mellon said that Venezuelas oil industry faces a long and difficult road to recovery, with meaningful production gains unlikely to materialize anytime soon.
+Speaking on the … [+2149 chars]</t>
+        </is>
+      </c>
+      <c r="G661" t="n">
+        <v>0.7783</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/russia-oil-flows-pivot-east-093000762.html</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Russia’s Oil Flows Pivot East as China Buys More and India Pulls Back</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Russia’s December oil exports surged on higher shipments to China while deliveries to India fell sharply, reflecting shifting trade patterns under sanctions ...</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Crude oil exports from Russia to China last month went up by 23% on the previous month, while exports to India declined by 29% on the month, Finnish Centre for Research on Energy and Clean Air said i… [+2209 chars]</t>
+        </is>
+      </c>
+      <c r="G662" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-maduros-ouster-will-have-limited-impact-on-gas-prices-as-they-sink-to-near-5-year-low-181123545.html</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Ines Ferré</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>2026-01-05T18:11:23Z</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Why Maduro's ouster will have 'limited' impact on gas prices as they sink to near 5-year low</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Regime change in Venezuela doesn't necessarily imply an immediate impact to oil supply and gas prices.</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Gasoline prices fell for a sixth straight week to their lowest level in nearly five years as seasonal factors and cheaper oil weighed on the market while traders monitored developments following the … [+2524 chars]</t>
+        </is>
+      </c>
+      <c r="G663" t="n">
+        <v>-0.4215</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bofa-raises-chevron-cvx-target-220621935.html</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Vardah Gill</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2026-01-30T22:06:21Z</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>BofA Raises Chevron (CVX) Target as Geopolitical Shifts Lift Energy Outlook</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 14 High Yield Dividend Stocks with Sustainable Payouts. On January 27, BofA lifted its price target on...</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 14 High Yield Dividend Stocks with Sustainable Payouts.
+BofA Raises Chevron (CVX) Target as Geopolitical Shifts Lift Energy Outlook
+On January 2… [+2338 chars]</t>
+        </is>
+      </c>
+      <c r="G664" t="n">
+        <v>0.4939</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-oil-capital-houston-buzzes-111221828.html</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar and Nathan  Crooks</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>2026-01-26T11:12:21Z</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>US oil capital Houston buzzes as industry limbers up for Venezuela oil rush</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar and Nathan Crooks HOUSTON, Jan 26 (Reuters) - In a downtown Houston bar, Matthew Goitia, a director at Pelorus Terminals, lays out his...</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar and Nathan Crooks
+HOUSTON, Jan 26 (Reuters) - In a downtown Houston bar, Matthew Goitia, a director at Pelorus Terminals, lays out his early idea to refurbish and build marine t… [+8807 chars]</t>
+        </is>
+      </c>
+      <c r="G665" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bernstein-raises-chevron-cvx-target-233016247.html</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Vardah Gill</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2026-01-08T23:30:16Z</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Bernstein Raises Chevron (CVX) Target as Oil Outlook Balances Volatility and Strength</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 12 Best DOW Stocks to Buy in 2026. On January 5, Bernstein raised its price target on Chevron...</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 12 Best DOW Stocks to Buy in 2026.
+Bernstein Raises Chevron (CVX) Target as Oil Outlook Balances Volatility and Strength
+Photo by Luis Ramirez o… [+1990 chars]</t>
+        </is>
+      </c>
+      <c r="G666" t="n">
+        <v>0.891</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-cenovus-energy-cve-fell-030040072.html</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>2026-01-09T03:00:40Z</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Here is Why Cenovus Energy (CVE) Fell This Week</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>The share price of Cenovus Energy Inc. (NYSE:CVE) fell by 6.32% between December 31, 2025, and January 7, 2026, putting it among the Energy Stocks that Lost ...</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>The share price of Cenovus Energy Inc. (NYSE:CVE) fell by 6.32% between December 31, 2025, and January 7, 2026, putting it among the Energy Stocks that Lost the Most This Week.
+Here is Why Cenovus E… [+1989 chars]</t>
+        </is>
+      </c>
+      <c r="G667" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_fb9daa03-fb5c-4503-ad5b-43006060a5f5</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr"/>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>2026-01-07T14:49:00Z</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>The last bearish overhang for crude — Venezuela — is now gone. Why one trader says oil will follow in gold’s footsteps.</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G668" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/devon-energy-dvn-price-target-030042907.html</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>2026-01-09T03:00:42Z</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Devon Energy (DVN) Price Target Lowered to $42, ‘Outperform’ Rating Maintained</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>The share price of Devon Energy Corporation (NYSE:DVN) fell by 5.9% between December 31, 2025, and January 7, 2026, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>The share price of Devon Energy Corporation (NYSE:DVN) fell by 5.9% between December 31, 2025, and January 7, 2026, putting it among the Energy Stocks that Lost the Most This Week.
+Devon Energy (DVN… [+1502 chars]</t>
+        </is>
+      </c>
+      <c r="G669" t="n">
+        <v>0.7003</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bernstein-trims-price-target-conocophillips-051229794.html</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>2026-01-08T05:12:29Z</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Bernstein Trims Price Target on ConocoPhillips (COP) by $18</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is included among the 10 Best Natural Gas Stocks to Buy Right Now. ConocoPhillips (NYSE:COP) is one of the world’s largest...</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is included among the 10 Best Natural Gas Stocks to Buy Right Now.
+Bernstein Trims Price Target on ConocoPhillips (COP) by $18
+ConocoPhillips (NYSE:COP) is one of the worl… [+1849 chars]</t>
+        </is>
+      </c>
+      <c r="G670" t="n">
+        <v>0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/cheap-oil-double-edged-sword-230000507.html</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>2026-01-12T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Cheap Oil Is Double-Edged Sword for Trump</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Oversupply fears have weighed on prices, with forecasters expecting production cuts from shale and falling upstream capex.</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>One of the campaign promises of President Donald Trump was to secure affordable energy for Americans. Even at the time, this promise put him at odds with the oil industry, already suffering from low … [+5543 chars]</t>
+        </is>
+      </c>
+      <c r="G671" t="n">
+        <v>0.5461</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-falls-exxon-chevron-don-000000985.html</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>2026-01-16T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>When Oil Falls but Exxon and Chevron Don’t</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Aggressive layoffs, efficiency gains, and exits from loss-making low-carbon ventures helped the five supermajors generate about $96 billion in free cash flow...</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Despite a 20% slump in oil prices in 2025, the world’s biggest international oil firms saw their stocks rise by 4% to 18%, breaking the correlation between crude prices and oil stocks.
+Last year, in… [+5886 chars]</t>
+        </is>
+      </c>
+      <c r="G672" t="n">
+        <v>-0.7227</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trumps-whiplash-iran-rhetoric-keeps-155200578.html</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>2026-01-30T15:52:00Z</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Trump's Whiplash Iran Rhetoric Keeps Oil Bulls in Control</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Markets looked past rising supply as shifting U.S. rhetoric on Iran and ongoing weather-related disruptions kept risk premiums elevated</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Markets looked past rising supply as shifting U.S. rhetoric on Iran and ongoing weather-related disruptions kept risk premiums elevated.
+Friday, January 30, 2026 
+Trumps erratic rhetoric has been g… [+4896 chars]</t>
+        </is>
+      </c>
+      <c r="G673" t="n">
+        <v>-0.5423</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/global-upstream-capex-set-fall-000000561.html</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2026-01-12T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Global Upstream Capex Set To Fall Again In 2026 Amid Low Oil Prices</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Producers prioritize capital discipline amid sub-$60 oil prices, with cuts in North America and Europe offsetting higher spending in the Middle East and...</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Last year, upstream oil investment was projected to have declined 2.5% Y/Y to $420 billion after low oil prices put pressure on producers and slowed expansion plans. Companies across the industry con… [+5185 chars]</t>
+        </is>
+      </c>
+      <c r="G674" t="n">
+        <v>-0.6597</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/delek-us-holdings-dk-price-101627812.html</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>2026-01-18T10:16:27Z</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Delek US Holdings (DK) Price Target Reduced by $6</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>The share price of Delek US Holdings, Inc. (NYSE:DK) fell by 9.6% between January 9 and January 16, 2026, putting it among the Energy Stocks that Lost the...</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>The share price of Delek US Holdings, Inc. (NYSE:DK) fell by 9.6% between January 9 and January 16, 2026, putting it among the Energy Stocks that Lost the Most This Week.
+ Delek US Holdings (DK) Pri… [+1600 chars]</t>
+        </is>
+      </c>
+      <c r="G675" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-signals-us-control-over-123300441.html</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Jing Pan</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>2026-01-07T12:33:00Z</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Trump signals US control over Venezuela’s oil worth $17T, the largest in the world. How to bet big on America in 2026</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Trump says U.S. oil companies are eager to get involved.</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Getty Images
+Moneywise and Yahoo Finance LLC may earn commission or revenue through links in the content below.
+After the capture of Venezuelan President Nicolás Maduro, U.S. President Donald Trump… [+7211 chars]</t>
+        </is>
+      </c>
+      <c r="G676" t="n">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/keybanc-downgrades-eog-resources-eog-122733041.html</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>2026-01-19T12:27:33Z</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>KeyBanc Downgrades EOG Resources (EOG) to Sector Weight, RBC Capital Lowers PT</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>EOG Resources, Inc. (NYSE:EOG) is one of the 12 Best American Energy Stocks to Buy Now. On January 16, KeyBanc downgraded its rating on EOG Resources, Inc. (...</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>EOG Resources, Inc. (NYSE:EOG) is one of the 12 Best American Energy Stocks to Buy Now. On January 16, KeyBanc downgraded its rating on EOG Resources, Inc. (NYSE:EOG) from Overweight to Sector Weight… [+1852 chars]</t>
+        </is>
+      </c>
+      <c r="G677" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/analyst-reiterates-buy-rating-devon-051235003.html</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>2026-01-08T05:12:35Z</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Analyst Reiterates ‘Buy’ Rating on Devon Energy (DVN)</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Devon Energy Corporation (NYSE:DVN) is included among the 10 Best Natural Gas Stocks to Buy Right Now. Devon Energy Corporation (NYSE:DVN) is a leading...</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Devon Energy Corporation (NYSE:DVN) is included among the 10 Best Natural Gas Stocks to Buy Right Now.
+Analyst Reiterates 'Buy' Rating on Devon Energy (DVN) 
+Devon Energy Corporation (NYSE:DVN) is … [+1895 chars]</t>
+        </is>
+      </c>
+      <c r="G678" t="n">
+        <v>0.9201</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/wall-street-bullish-scorpio-tankers-052423358.html</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Jabran Kundi</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>2026-01-14T05:24:23Z</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Wall Street Bullish on Scorpio Tankers (STNG) as Company Signs New Charter Agreements</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Scorpio Tankers Inc. (NYSE:STNG) is one of the 10 cheapest oil and gas stocks to invest in. According to the company’s announcement dated January 5, it has...</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Scorpio Tankers Inc. (NYSE:STNG) is one of the 10 cheapest oil and gas stocks to invest in. According to the companys announcement dated January 5, it has entered into five-year time charter agreemen… [+1836 chars]</t>
+        </is>
+      </c>
+      <c r="G679" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/40-us-oil-jobs-lost-103032384.html</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Julia Fanzeres and Will Kubzansky</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>2026-01-16T10:30:32Z</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>The 40% of US Oil Jobs Lost Over the Last Decade Aren't Coming Back</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>In an industry known for its booms and busts, higher oil prices have historically spurred greater drilling activity, and therefore more hiring.  In the years...</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Photographer: Eli Hartman/Bloomberg
+(Bloomberg) -- The US oil and gas industry slashed 40% of its workforce over the past decade of record-breaking production and those jobs are unlikely to return.
+… [+5485 chars]</t>
+        </is>
+      </c>
+      <c r="G680" t="n">
+        <v>-0.4939</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/could-civitas-resources-civi-finally-052414800.html</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Jabran Kundi</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>2026-01-14T05:24:14Z</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Could Civitas Resources (CIVI) Finally Take Off After Regulatory Clarity?</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Civitas Resources, Inc. (NYSE:CIVI) is one of the 10 cheapest oil and gas stocks to invest in. Siebert Williams Shank &amp; Co reaffirmed its Hold rating on the ...</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Civitas Resources, Inc. (NYSE:CIVI) is one of the 10 cheapest oil and gas stocks to invest in. Siebert Williams Shank &amp;amp; Co reaffirmed its Hold rating on the stock on December 26. Gabriele Sorbara… [+1969 chars]</t>
+        </is>
+      </c>
+      <c r="G681" t="n">
+        <v>0.4019</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_0c8aa00a-70f6-468c-91ef-56fcf78170ca</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>2026-01-26T20:01:25Z</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Crude Oil Falls Back as Kazakhstan's Oil Disruptions Ease</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G682" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_9d24873a-b4b2-41b1-8e06-6cc28d78eada</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr"/>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>2026-01-13T20:22:09Z</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Geopolitical Risks Underpin Crude Oil Prices</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr"/>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G683" t="n">
+        <v>-0.3182</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_0f891552-b8a6-40e4-9762-051f77c9588f</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr"/>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>2026-01-21T20:25:15Z</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Crude Oil Gains on Iran Risks</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G684" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-edge-down-as-jobs-data-trumps-venezuela-oil-deal-take-focus-002323719.html</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>2026-01-07T00:23:23Z</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq edge down as jobs data, Trump's Venezuela oil deal take focus</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Markets are holding steady after a roaring start to the week, with Venezuela, CES, and jobs data releases all in focus.</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>US stock futures tilted lower on Wednesday, backing away from record highs as investors absorbed a promised deal to send Venezuela oil to the US and waited for fresh jobs data to lead in the all-impo… [+6200 chars]</t>
+        </is>
+      </c>
+      <c r="G685" t="n">
+        <v>0.4019</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_86e009e3-8cb8-40b9-8af5-0832f2b824e5</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr"/>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>2026-01-11T16:25:08Z</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Are Crude Oil Markets Bullish Now?</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G686" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_f61e5a99-9183-4e1c-ae39-4d03ca935e58</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr"/>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>2026-01-16T20:22:35Z</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Iran Tensions Underpin Crude Oil Prices</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G687" t="n">
+        <v>-0.4404</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-jump-to-records-nasdaq-surges-as-stocks-end-2026s-first-week-with-big-gains-210029649.html</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>2026-01-09T21:00:29Z</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500 jump to records, Nasdaq surges as stocks end 2026's first week with big gains</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Payrolls data cements view the Fed won't cut, as focus turns to a potential Supreme Court ruling on tariffs.</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>In a meeting with oil industry leaders at the White House on Friday, President Trump said the US industry will be "spending at least $100 billion of their own money ... to rebuild the capacity and th… [+2260 chars]</t>
+        </is>
+      </c>
+      <c r="G688" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/scotiabank-lowers-eog-resources-eog-030009986.html</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>2026-01-23T03:00:09Z</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Scotiabank Lowers EOG Resources (EOG) PT to $123, Cites Stable Production, Sector-Wide Adjustments</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>EOG Resources Inc. (NYSE:EOG) is one of the best large cap value stocks to buy in 2026. On January 16, Scotiabank analyst Paul Cheng lowered the firm’s price...</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>EOG Resources Inc. (NYSE:EOG) is one of the best large cap value stocks to buy in 2026. On January 16, Scotiabank analyst Paul Cheng lowered the firms price target on EOG Resources to $123 from $130 … [+1699 chars]</t>
+        </is>
+      </c>
+      <c r="G689" t="n">
+        <v>0.7783</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/asian-shares-mostly-lower-oil-044124151.html</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>STAN CHOE</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:41:24Z</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Wall Street steadies as chip stocks bounce back and oil prices ease</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Wall Street steadied on Thursday as stocks in the artificial-intelligence industry bounced back following an encouraging report from a Taiwanese chip giant  ...</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>NEW YORK (AP) Wall Street steadied on Thursday as stocks in the artificial-intelligence industry bounced back following an encouraging report from a Taiwanese chip giant and as oil prices eased sharp… [+3976 chars]</t>
+        </is>
+      </c>
+      <c r="G690" t="n">
+        <v>0.7964</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-market-watch-venezuela-raid-191643822.html</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Bibhu Pattnaik</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>2026-01-04T19:16:43Z</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Oil Is Market To Watch as Venezuela Raid Raises Stakes</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>The US raid on Venezuela could significantly impact the oil market. The price of crude oil, which directly influences American consumer prices at the pump...</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>The US raid on Venezuela could significantly impact the oil market. The price of crude oil, which directly influences American consumer prices at the pump, is expected to be a key focus in the afterm… [+2168 chars]</t>
+        </is>
+      </c>
+      <c r="G691" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/us-oilfield-firm-slb-says-172505189.html</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar and Tanay Dhumal</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>2026-01-23T17:25:05Z</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>US oilfield service firm SLB says it can rapidly boost Venezuela operations</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>oilfield service company SLB said on Friday it can rapidly increase its activities in Venezuela, provided the appropriate licensing, safety parameters and...</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>By Arathy Somasekhar and Tanay Dhumal
+HOUSTON, Jan 23 (Reuters) - U.S. oilfield service company SLB said on Friday it can rapidly increase its activities in Venezuela, provided the appropriate licen… [+2426 chars]</t>
+        </is>
+      </c>
+      <c r="G692" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-waver-as-jobs-data-trumps-venezuela-oil-deal-take-focus-002323425.html</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>2026-01-07T00:23:23Z</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq waver as jobs data, Trump's Venezuela oil deal take focus</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Markets are holding steady after a roaring start to the week, with Venezuela, CES, and jobs data releases all in focus.</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>US stock futures wobbled on Wednesday, backing away from record highs as investors absorbed a promised deal to send Venezuela oil to the US and digested fresh jobs data that will lead in the all-impo… [+9240 chars]</t>
+        </is>
+      </c>
+      <c r="G693" t="n">
+        <v>0.5994</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/analysts-stay-positive-chevron-cvx-122718690.html</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>2026-01-19T12:27:18Z</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Analysts Stay Positive on Chevron (CVX) Despite Challenges</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is one of the 12 Best American Energy Stocks to Buy Now. On January 14, Jefferies raised its price target on Chevron...</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is one of the 12 Best American Energy Stocks to Buy Now. On January 14, Jefferies raised its price target on Chevron Corporation (NYSE:CVX) from $174 to $189 and mainta… [+1831 chars]</t>
+        </is>
+      </c>
+      <c r="G694" t="n">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_e1ac0c1d-e919-4f0d-adc0-c875bcb4e651</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr"/>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>2026-01-29T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>China’s Crude Hoarding Is Propping Up Oil Prices</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G695" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-venezuela-oil-dream-meets-000000688.html</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>2026-01-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Trump’s Venezuela Oil Dream Meets a $100 Billion Reality Check</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>While Washington is urging U.S. firms to re-enter Venezuela and heavy crude is in strong demand, companies remain wary.</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>The shock-and-awe capture of Nicolas Maduro by the United States, which was the culmination of the U.S. pressure on Venezuela in recent months, ended a tumultuous chapter in the history of the South … [+4584 chars]</t>
+        </is>
+      </c>
+      <c r="G696" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-rise-as-techs-revive-while-oil-majors-jump-after-us-strike-in-venezuela-235634967.html</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>2026-01-04T23:56:34Z</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as techs revive, while oil majors jump after US strike in Venezuela</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Wall Street is assessing the US military strike and capture of President Maduro in Venezuela, while hopes for AI demand buoy techs.</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>US stocks rose on Monday amid gains for oil stocks after the US military strike and capture of President Maduro in Venezuela, while a revival in optimism for AI demand buoyed tech names.
+The blue ch… [+2386 chars]</t>
+        </is>
+      </c>
+      <c r="G697" t="n">
+        <v>0.7003</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chord-energy-corporation-chrd-bull-151341545.html</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Ricardo Pillai</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>2026-01-20T15:13:41Z</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Chord Energy Corporation (CHRD): A Bull Case Theory</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Chord Energy Corporation on r/Valueinvesting by pandacrusher63. In this article, we will summarize the bulls’ thesis on...</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Chord Energy Corporation on r/Valueinvesting by pandacrusher63. In this article, we will summarize the bulls thesis on CHRD. Chord Energy Corporation's share was tr… [+2631 chars]</t>
+        </is>
+      </c>
+      <c r="G698" t="n">
+        <v>0.7579</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/saudi-stocks-drop-most-since-133835178.html</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Christine Burke</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>2026-01-04T13:38:35Z</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Saudi stocks drop most since April as geopolitical strife mounts</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>The Tadawul All Share Index dropped 1.8% on Sunday, the most since US President Donald Trump’s tariffs roiled global markets in April, with all industry...</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>(Bloomberg) Saudi Arabian equities fell the most in almost nine months as investors considered the possible fallout of geopolitical tensions in Yemen, Iran and Venezuela.
+The Tadawul All Share Index… [+1703 chars]</t>
+        </is>
+      </c>
+      <c r="G699" t="n">
+        <v>-0.3818</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/asian-benchmarks-mixed-wall-street-040952978.html</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>STAN CHOE</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>2026-01-14T04:09:52Z</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Wall Street slumps as bank and tech stocks fall</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Losses for several banks and Big Tech stocks pulled indexes lower on Wednesday, even though the majority of stocks on Wall Street rose.  Citigroup, which is ...</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>NEW YORK (AP) Losses for several banks and Big Tech stocks pulled indexes lower on Wednesday, even though the majority of stocks on Wall Street rose.
+The S&amp;amp;P 500 slipped 0.5% for its second stra… [+3801 chars]</t>
+        </is>
+      </c>
+      <c r="G700" t="n">
+        <v>-0.5994</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chevron-cvx-talks-expand-oil-205238211.html</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>2026-01-13T20:52:38Z</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Chevron (CVX) in Talks to Expand Oil License in Venezuela</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 10 High Yield Crude Oil Stocks to Buy After Trump’s Blitz in Venezuela. Chevron Corporation (NYSE:CVX...</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 10 High Yield Crude Oil Stocks to Buy After Trump's Blitz in Venezuela.
+Chevron (CVX) in Talks to Expand Oil License in Venezuela
+Chevron Corpor… [+2139 chars]</t>
+        </is>
+      </c>
+      <c r="G701" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-oil-imports-hit-time-063000971.html</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>2026-01-14T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>China’s Oil Imports Hit an All-Time High in 2025</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>China’s crude oil imports reached a record high last year, driven by aggressive stockpiling that challenges assumptions of irreversible demand decline amid...</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Crude oil imports into China last year hit the highest ever, reaching 11.55 million barrels daily, or a total of 557.73 million tons, up 4.4% on 2024, Reuters reported today, citing official statisti… [+2200 chars]</t>
+        </is>
+      </c>
+      <c r="G702" t="n">
+        <v>-0.4404</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-sp-500-nasdaq-nudge-up-but-dow-lags-as-jobs-data-trumps-venezuela-oil-deal-take-focus-002323778.html</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>2026-01-07T00:23:23Z</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Stock market today: S&amp;P 500, Nasdaq nudge up but Dow lags as jobs data, Trump's Venezuela oil deal take focus</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>The S&amp;P 500 is eyeing a fresh record after a roaring start to the week, with Venezuela, CES, and jobs data releases all in focus.</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>US stocks mostly edged up on Wednesday, headed for all-time highs as investors absorbed a promised deal to send Venezuelan oil to the US and digested fresh jobs data leading into the all-important mo… [+9936 chars]</t>
+        </is>
+      </c>
+      <c r="G703" t="n">
+        <v>0.4497</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/hf-sinclair-dino-completes-acquisition-205340180.html</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>2026-01-13T20:53:40Z</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>HF Sinclair (DINO) Completes Acquisition of Industrial Oils Unlimited</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>HF Sinclair Corporation (NYSE:DINO) is included among the 10 High Yield Crude Oil Stocks to Buy After Trump’s Blitz in Venezuela. HF Sinclair Corporation...</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>HF Sinclair Corporation (NYSE:DINO) is included among the 10 High Yield Crude Oil Stocks to Buy After Trump's Blitz in Venezuela.
+HF Sinclair (DINO) Completes Acquisition of Industrial Oils Unlimite… [+2359 chars]</t>
+        </is>
+      </c>
+      <c r="G704" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/market-minute-1-20-26-141500330.html</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>MoneyShow</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2026-01-20T14:15:00Z</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Market Minute 1-20-26- Greenland Battle, Bond Rout Roil Markets</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Stocks and bonds are selling off sharply, while precious metals are on fire. The US dollar is sharply lower, while crude oil is up modestly.</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Stocks and bonds are selling off sharply, while precious metals are on fire. The US dollar is sharply lower, while crude oil is up modestly.
+To get your FREE copy of the complete MoneyShow 2026 Top … [+1717 chars]</t>
+        </is>
+      </c>
+      <c r="G705" t="n">
+        <v>-0.09429999999999999</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venezuela-says-it-has-the-worlds-largest-reserves-of-crude-oil-making-it-viable-is-a-whole-other-problem-181512098.html</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Jake Conley</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>2026-01-06T18:15:12Z</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Venezuela says it has the world's largest reserves of crude oil. Making it viable is a whole other problem.</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Venezuela says it sits on the world's largest commercially viable oil reserves. Even if that claim is shaky, the challenges for getting this oil to market...</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Despite exporting less than 1% of the world's supply of oil, Venezuela has been a key focal point in the energy market for decades.
+Why? Because the country claims to have the largest reserves of cr… [+6978 chars]</t>
+        </is>
+      </c>
+      <c r="G706" t="n">
+        <v>-0.6486</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-sp-500-dow-nasdaq-mixed-as-cpi-inflation-eases-jpmorgan-kicks-off-earnings-234952160.html</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>2026-01-12T23:49:52Z</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Stock market today: S&amp;P 500, Dow, Nasdaq mixed as CPI inflation eases, JPMorgan kicks off earnings</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Wall Street is reacting to "core" CPI coming in below expectations against a backdrop of local and foreign political disruption.</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>US stocks traded mixed on Tuesday as a milder inflation reading supported bets that the Fed will hold rates steady, while JPMorgan (JPM) results kicked off the fourth quarter earnings season.
+The bl… [+10142 chars]</t>
+        </is>
+      </c>
+      <c r="G707" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-futures-waver-as-cpi-inflation-eases-jpmorgan-kicks-off-earnings-234952642.html</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>2026-01-12T23:49:52Z</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures waver as CPI inflation eases, JPMorgan kicks off earnings</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Wall Street is bracing for a CPI report against a backdrop of local and foreign political disruption.</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>US stock futures wavered before the bell Tuesday as a milder inflation reading kept bets that the Fed would hold rates steady intact, while JPMorgan (JPM) results kicked off the fourth quarter earnin… [+9203 chars]</t>
+        </is>
+      </c>
+      <c r="G708" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-sp-500-nasdaq-rise-after-us-takedown-in-venezuela-as-ai-hopes-revive-235634319.html</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>2026-01-04T23:56:34Z</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Stock market today: S&amp;P 500, Nasdaq rise after US takedown in Venezuela as AI hopes revive</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>The US military action in Venezuela early into the weekend took focus as markets headed into the first full trading week of the new year.</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>US stocks rose on Monday as investors assessed the US military operation in Venezuela that led to the capture of President Nicolás Maduro, while a revival in optimism for AI demand helped buoy Wall S… [+6920 chars]</t>
+        </is>
+      </c>
+      <c r="G709" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trumps-move-seize-control-venezuela-201055355.html</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>David Okoya</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>2026-01-08T20:10:55Z</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Trump's Move To Seize Control of Venezuela Means 'Bitcoin And Certain Cryptos Will Skyrocket,' Arthur Hayes Says</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>President Donald Trump‘s Venezuela gambit is bullish for Bitcoin, BitMEX founder and Maelstrom investment chief Arthur Hayes says. “The price of Bitcoin and ...</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Benzinga and Yahoo Finance LLC may earn commission or revenue on some items through the links below.
+President Donald Trumps Venezuela gambit is bullish for Bitcoin, BitMEX founder and Maelstrom inv… [+9133 chars]</t>
+        </is>
+      </c>
+      <c r="G710" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
